--- a/source-excel/CPK.xlsx
+++ b/source-excel/CPK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\newstarrating\source-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6646C8-14A9-4427-B82C-572E5E6E92DB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F289D415-64EF-4F85-9295-939C9E20A337}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" xr2:uid="{A8A91EEF-99CC-4EB3-BE03-3D899D5B1C9B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" activeTab="1" xr2:uid="{A8A91EEF-99CC-4EB3-BE03-3D899D5B1C9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Q" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="Manual" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Q!$A$1:$Q$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Q!$A$1:$Q$291</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Q-Score'!$A$1:$S$292</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3524,6 +3525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B51C6DEB-D6D2-4541-A2C9-F907FBFFFC48}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q291"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.6"/>
   <cols>
@@ -3589,7 +3591,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A2" s="4" t="s">
         <v>44</v>
       </c>
@@ -3642,7 +3644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A3" s="4" t="s">
         <v>44</v>
       </c>
@@ -3695,7 +3697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A4" s="4" t="s">
         <v>44</v>
       </c>
@@ -3748,7 +3750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
@@ -3801,7 +3803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A6" s="4" t="s">
         <v>45</v>
       </c>
@@ -3854,7 +3856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A7" s="4" t="s">
         <v>45</v>
       </c>
@@ -3907,7 +3909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A8" s="4" t="s">
         <v>45</v>
       </c>
@@ -3960,7 +3962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A9" s="4" t="s">
         <v>45</v>
       </c>
@@ -4013,7 +4015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A10" s="4" t="s">
         <v>45</v>
       </c>
@@ -4066,7 +4068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A11" s="4" t="s">
         <v>45</v>
       </c>
@@ -4119,7 +4121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
@@ -4172,7 +4174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A13" s="4" t="s">
         <v>45</v>
       </c>
@@ -4225,7 +4227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A14" s="4" t="s">
         <v>45</v>
       </c>
@@ -4278,7 +4280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A15" s="4" t="s">
         <v>45</v>
       </c>
@@ -4331,7 +4333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
@@ -4384,7 +4386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A17" s="4" t="s">
         <v>45</v>
       </c>
@@ -4437,7 +4439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A18" s="4" t="s">
         <v>45</v>
       </c>
@@ -4490,7 +4492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A19" s="4" t="s">
         <v>45</v>
       </c>
@@ -4543,7 +4545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A20" s="4" t="s">
         <v>45</v>
       </c>
@@ -4596,7 +4598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A21" s="4" t="s">
         <v>45</v>
       </c>
@@ -4649,7 +4651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A22" s="4" t="s">
         <v>45</v>
       </c>
@@ -4702,7 +4704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A23" s="4" t="s">
         <v>45</v>
       </c>
@@ -4755,7 +4757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A24" s="4" t="s">
         <v>45</v>
       </c>
@@ -4808,7 +4810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A25" s="4" t="s">
         <v>45</v>
       </c>
@@ -4861,7 +4863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A26" s="4" t="s">
         <v>45</v>
       </c>
@@ -4914,7 +4916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A27" s="4" t="s">
         <v>45</v>
       </c>
@@ -4967,7 +4969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A28" s="4" t="s">
         <v>45</v>
       </c>
@@ -5020,7 +5022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A29" s="4" t="s">
         <v>45</v>
       </c>
@@ -5073,7 +5075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A30" s="4" t="s">
         <v>45</v>
       </c>
@@ -5126,7 +5128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A31" s="4" t="s">
         <v>45</v>
       </c>
@@ -5179,7 +5181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A32" s="4" t="s">
         <v>45</v>
       </c>
@@ -5232,7 +5234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A33" s="4" t="s">
         <v>45</v>
       </c>
@@ -5285,7 +5287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A34" s="4" t="s">
         <v>45</v>
       </c>
@@ -5338,7 +5340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A35" s="4" t="s">
         <v>45</v>
       </c>
@@ -5391,7 +5393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A36" s="4" t="s">
         <v>45</v>
       </c>
@@ -5444,7 +5446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A37" s="4" t="s">
         <v>45</v>
       </c>
@@ -5497,7 +5499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A38" s="4" t="s">
         <v>45</v>
       </c>
@@ -5550,7 +5552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A39" s="4" t="s">
         <v>45</v>
       </c>
@@ -5603,7 +5605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A40" s="4" t="s">
         <v>45</v>
       </c>
@@ -5709,7 +5711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A42" s="4" t="s">
         <v>45</v>
       </c>
@@ -5762,7 +5764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A43" s="4" t="s">
         <v>45</v>
       </c>
@@ -5815,7 +5817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A44" s="4" t="s">
         <v>45</v>
       </c>
@@ -5868,7 +5870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A45" s="4" t="s">
         <v>45</v>
       </c>
@@ -5921,7 +5923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A46" s="4" t="s">
         <v>45</v>
       </c>
@@ -5974,7 +5976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A47" s="4" t="s">
         <v>46</v>
       </c>
@@ -6027,7 +6029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A48" s="4" t="s">
         <v>46</v>
       </c>
@@ -6080,7 +6082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A49" s="4" t="s">
         <v>46</v>
       </c>
@@ -6133,7 +6135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A50" s="4" t="s">
         <v>46</v>
       </c>
@@ -6186,7 +6188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A51" s="4" t="s">
         <v>46</v>
       </c>
@@ -6239,7 +6241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A52" s="4" t="s">
         <v>46</v>
       </c>
@@ -6292,7 +6294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A53" s="4" t="s">
         <v>46</v>
       </c>
@@ -6345,7 +6347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A54" s="4" t="s">
         <v>46</v>
       </c>
@@ -6398,7 +6400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A55" s="4" t="s">
         <v>46</v>
       </c>
@@ -6451,7 +6453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A56" s="4" t="s">
         <v>46</v>
       </c>
@@ -6504,7 +6506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A57" s="4" t="s">
         <v>46</v>
       </c>
@@ -6557,7 +6559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A58" s="4" t="s">
         <v>46</v>
       </c>
@@ -6610,7 +6612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A59" s="4" t="s">
         <v>46</v>
       </c>
@@ -6663,7 +6665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A60" s="4" t="s">
         <v>46</v>
       </c>
@@ -6716,7 +6718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A61" s="4" t="s">
         <v>46</v>
       </c>
@@ -6769,7 +6771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A62" s="4" t="s">
         <v>46</v>
       </c>
@@ -6822,7 +6824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A63" s="4" t="s">
         <v>46</v>
       </c>
@@ -6875,7 +6877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A64" s="4" t="s">
         <v>46</v>
       </c>
@@ -6928,7 +6930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A65" s="4" t="s">
         <v>46</v>
       </c>
@@ -6981,7 +6983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A66" s="4" t="s">
         <v>46</v>
       </c>
@@ -7034,7 +7036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A67" s="4" t="s">
         <v>47</v>
       </c>
@@ -7087,7 +7089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A68" s="4" t="s">
         <v>47</v>
       </c>
@@ -7140,7 +7142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A69" s="4" t="s">
         <v>47</v>
       </c>
@@ -7193,7 +7195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A70" s="4" t="s">
         <v>47</v>
       </c>
@@ -7246,7 +7248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A71" s="4" t="s">
         <v>47</v>
       </c>
@@ -7299,7 +7301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A72" s="4" t="s">
         <v>47</v>
       </c>
@@ -7352,7 +7354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A73" s="4" t="s">
         <v>47</v>
       </c>
@@ -7405,7 +7407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A74" s="4" t="s">
         <v>47</v>
       </c>
@@ -7458,7 +7460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A75" s="4" t="s">
         <v>47</v>
       </c>
@@ -7511,7 +7513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A76" s="4" t="s">
         <v>47</v>
       </c>
@@ -7564,7 +7566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A77" s="4" t="s">
         <v>47</v>
       </c>
@@ -7617,7 +7619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A78" s="4" t="s">
         <v>47</v>
       </c>
@@ -7670,7 +7672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A79" s="4" t="s">
         <v>47</v>
       </c>
@@ -7723,7 +7725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A80" s="4" t="s">
         <v>47</v>
       </c>
@@ -7776,7 +7778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A81" s="4" t="s">
         <v>47</v>
       </c>
@@ -7829,7 +7831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A82" s="4" t="s">
         <v>47</v>
       </c>
@@ -7882,7 +7884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A83" s="4" t="s">
         <v>47</v>
       </c>
@@ -7935,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A84" s="4" t="s">
         <v>47</v>
       </c>
@@ -7988,7 +7990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A85" s="4" t="s">
         <v>47</v>
       </c>
@@ -8041,7 +8043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A86" s="4" t="s">
         <v>47</v>
       </c>
@@ -8094,7 +8096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A87" s="4" t="s">
         <v>47</v>
       </c>
@@ -8147,7 +8149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A88" s="4" t="s">
         <v>47</v>
       </c>
@@ -8200,7 +8202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A89" s="4" t="s">
         <v>47</v>
       </c>
@@ -8253,7 +8255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A90" s="4" t="s">
         <v>47</v>
       </c>
@@ -8306,7 +8308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A91" s="4" t="s">
         <v>47</v>
       </c>
@@ -8359,7 +8361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A92" s="4" t="s">
         <v>47</v>
       </c>
@@ -8412,7 +8414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A93" s="4" t="s">
         <v>47</v>
       </c>
@@ -8465,7 +8467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A94" s="4" t="s">
         <v>47</v>
       </c>
@@ -8518,7 +8520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A95" s="4" t="s">
         <v>47</v>
       </c>
@@ -8571,7 +8573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A96" s="4" t="s">
         <v>47</v>
       </c>
@@ -8624,7 +8626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A97" s="4" t="s">
         <v>47</v>
       </c>
@@ -8677,7 +8679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A98" s="4" t="s">
         <v>47</v>
       </c>
@@ -8730,7 +8732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A99" s="4" t="s">
         <v>47</v>
       </c>
@@ -8783,7 +8785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A100" s="4" t="s">
         <v>47</v>
       </c>
@@ -8836,7 +8838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A101" s="4" t="s">
         <v>47</v>
       </c>
@@ -8889,7 +8891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A102" s="4" t="s">
         <v>47</v>
       </c>
@@ -8942,7 +8944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A103" s="4" t="s">
         <v>47</v>
       </c>
@@ -8995,7 +8997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A104" s="4" t="s">
         <v>47</v>
       </c>
@@ -9048,7 +9050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A105" s="4" t="s">
         <v>47</v>
       </c>
@@ -9101,7 +9103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A106" s="4" t="s">
         <v>47</v>
       </c>
@@ -9154,7 +9156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A107" s="4" t="s">
         <v>47</v>
       </c>
@@ -9207,7 +9209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A108" s="4" t="s">
         <v>47</v>
       </c>
@@ -9260,7 +9262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A109" s="4" t="s">
         <v>47</v>
       </c>
@@ -9313,7 +9315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A110" s="4" t="s">
         <v>47</v>
       </c>
@@ -9366,7 +9368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A111" s="4" t="s">
         <v>47</v>
       </c>
@@ -9419,7 +9421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A112" s="4" t="s">
         <v>47</v>
       </c>
@@ -9472,7 +9474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A113" s="4" t="s">
         <v>47</v>
       </c>
@@ -9525,7 +9527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A114" s="4" t="s">
         <v>47</v>
       </c>
@@ -9578,7 +9580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A115" s="4" t="s">
         <v>47</v>
       </c>
@@ -9631,7 +9633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A116" s="4" t="s">
         <v>47</v>
       </c>
@@ -9684,7 +9686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A117" s="4" t="s">
         <v>47</v>
       </c>
@@ -9737,7 +9739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A118" s="4" t="s">
         <v>47</v>
       </c>
@@ -9790,7 +9792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A119" s="4" t="s">
         <v>47</v>
       </c>
@@ -9843,7 +9845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A120" s="4" t="s">
         <v>47</v>
       </c>
@@ -9896,7 +9898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A121" s="4" t="s">
         <v>47</v>
       </c>
@@ -9949,7 +9951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A122" s="4" t="s">
         <v>47</v>
       </c>
@@ -10002,7 +10004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A123" s="4" t="s">
         <v>47</v>
       </c>
@@ -10055,7 +10057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A124" s="4" t="s">
         <v>47</v>
       </c>
@@ -10108,7 +10110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A125" s="4" t="s">
         <v>47</v>
       </c>
@@ -10161,7 +10163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A126" s="4" t="s">
         <v>47</v>
       </c>
@@ -10214,7 +10216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A127" s="4" t="s">
         <v>47</v>
       </c>
@@ -10267,7 +10269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A128" s="4" t="s">
         <v>47</v>
       </c>
@@ -10320,7 +10322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A129" s="4" t="s">
         <v>47</v>
       </c>
@@ -10373,7 +10375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A130" s="4" t="s">
         <v>47</v>
       </c>
@@ -10426,7 +10428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A131" s="4" t="s">
         <v>47</v>
       </c>
@@ -10479,7 +10481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A132" s="4" t="s">
         <v>47</v>
       </c>
@@ -10532,7 +10534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A133" s="4" t="s">
         <v>47</v>
       </c>
@@ -10585,7 +10587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A134" s="4" t="s">
         <v>47</v>
       </c>
@@ -10638,7 +10640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A135" s="4" t="s">
         <v>47</v>
       </c>
@@ -10691,7 +10693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A136" s="4" t="s">
         <v>47</v>
       </c>
@@ -10744,7 +10746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A137" s="4" t="s">
         <v>47</v>
       </c>
@@ -10797,7 +10799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A138" s="4" t="s">
         <v>919</v>
       </c>
@@ -10850,7 +10852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A139" s="4" t="s">
         <v>919</v>
       </c>
@@ -10903,7 +10905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A140" s="4" t="s">
         <v>919</v>
       </c>
@@ -10956,7 +10958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A141" s="4" t="s">
         <v>919</v>
       </c>
@@ -11009,7 +11011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A142" s="4" t="s">
         <v>919</v>
       </c>
@@ -11062,7 +11064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A143" s="4" t="s">
         <v>919</v>
       </c>
@@ -11115,7 +11117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A144" s="4" t="s">
         <v>919</v>
       </c>
@@ -11168,7 +11170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A145" s="4" t="s">
         <v>919</v>
       </c>
@@ -11221,7 +11223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A146" s="4" t="s">
         <v>919</v>
       </c>
@@ -11274,7 +11276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A147" s="4" t="s">
         <v>919</v>
       </c>
@@ -11327,7 +11329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A148" s="4" t="s">
         <v>919</v>
       </c>
@@ -11380,7 +11382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A149" s="4" t="s">
         <v>919</v>
       </c>
@@ -11433,7 +11435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A150" s="4" t="s">
         <v>919</v>
       </c>
@@ -11486,7 +11488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A151" s="4" t="s">
         <v>919</v>
       </c>
@@ -11539,7 +11541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A152" s="4" t="s">
         <v>919</v>
       </c>
@@ -11592,7 +11594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A153" s="4" t="s">
         <v>919</v>
       </c>
@@ -11645,7 +11647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A154" s="4" t="s">
         <v>919</v>
       </c>
@@ -11698,7 +11700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A155" s="4" t="s">
         <v>919</v>
       </c>
@@ -11751,7 +11753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A156" s="4" t="s">
         <v>919</v>
       </c>
@@ -11804,7 +11806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A157" s="4" t="s">
         <v>919</v>
       </c>
@@ -11857,7 +11859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A158" s="4" t="s">
         <v>919</v>
       </c>
@@ -11910,7 +11912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A159" s="4" t="s">
         <v>919</v>
       </c>
@@ -11963,7 +11965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A160" s="4" t="s">
         <v>919</v>
       </c>
@@ -12016,7 +12018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A161" s="4" t="s">
         <v>919</v>
       </c>
@@ -12069,7 +12071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A162" s="4" t="s">
         <v>919</v>
       </c>
@@ -12122,7 +12124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A163" s="4" t="s">
         <v>919</v>
       </c>
@@ -12175,7 +12177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A164" s="4" t="s">
         <v>919</v>
       </c>
@@ -12228,7 +12230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A165" s="4" t="s">
         <v>919</v>
       </c>
@@ -12281,7 +12283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A166" s="4" t="s">
         <v>919</v>
       </c>
@@ -12334,7 +12336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A167" s="4" t="s">
         <v>919</v>
       </c>
@@ -12387,7 +12389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A168" s="4" t="s">
         <v>919</v>
       </c>
@@ -12440,7 +12442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A169" s="4" t="s">
         <v>919</v>
       </c>
@@ -12493,7 +12495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A170" s="4" t="s">
         <v>919</v>
       </c>
@@ -12546,7 +12548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A171" s="4" t="s">
         <v>919</v>
       </c>
@@ -12599,7 +12601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A172" s="4" t="s">
         <v>919</v>
       </c>
@@ -12652,7 +12654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A173" s="4" t="s">
         <v>919</v>
       </c>
@@ -12705,7 +12707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A174" s="4" t="s">
         <v>919</v>
       </c>
@@ -12758,7 +12760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A175" s="4" t="s">
         <v>919</v>
       </c>
@@ -12811,7 +12813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A176" s="4" t="s">
         <v>919</v>
       </c>
@@ -12864,7 +12866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A177" s="4" t="s">
         <v>919</v>
       </c>
@@ -12917,7 +12919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A178" s="4" t="s">
         <v>919</v>
       </c>
@@ -12970,7 +12972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A179" s="4" t="s">
         <v>919</v>
       </c>
@@ -13023,7 +13025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A180" s="4" t="s">
         <v>919</v>
       </c>
@@ -13076,7 +13078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A181" s="4" t="s">
         <v>919</v>
       </c>
@@ -13129,7 +13131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A182" s="4" t="s">
         <v>919</v>
       </c>
@@ -13182,7 +13184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A183" s="4" t="s">
         <v>919</v>
       </c>
@@ -13235,7 +13237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A184" s="4" t="s">
         <v>919</v>
       </c>
@@ -13288,7 +13290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A185" s="4" t="s">
         <v>919</v>
       </c>
@@ -13341,7 +13343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A186" s="4" t="s">
         <v>919</v>
       </c>
@@ -13394,7 +13396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A187" s="4" t="s">
         <v>919</v>
       </c>
@@ -13447,7 +13449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A188" s="4" t="s">
         <v>919</v>
       </c>
@@ -13500,7 +13502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A189" s="4" t="s">
         <v>919</v>
       </c>
@@ -13553,7 +13555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A190" s="4" t="s">
         <v>919</v>
       </c>
@@ -13606,7 +13608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A191" s="4" t="s">
         <v>919</v>
       </c>
@@ -13659,7 +13661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A192" s="4" t="s">
         <v>919</v>
       </c>
@@ -13712,7 +13714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A193" s="4" t="s">
         <v>919</v>
       </c>
@@ -13765,7 +13767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A194" s="4" t="s">
         <v>919</v>
       </c>
@@ -13818,7 +13820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A195" s="4" t="s">
         <v>919</v>
       </c>
@@ -13871,7 +13873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A196" s="4" t="s">
         <v>919</v>
       </c>
@@ -13924,7 +13926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A197" s="4" t="s">
         <v>919</v>
       </c>
@@ -13977,7 +13979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A198" s="4" t="s">
         <v>919</v>
       </c>
@@ -14030,7 +14032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A199" s="4" t="s">
         <v>919</v>
       </c>
@@ -14083,7 +14085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A200" s="4" t="s">
         <v>919</v>
       </c>
@@ -14136,7 +14138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A201" s="4" t="s">
         <v>919</v>
       </c>
@@ -14189,7 +14191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A202" s="4" t="s">
         <v>919</v>
       </c>
@@ -14242,7 +14244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A203" s="4" t="s">
         <v>919</v>
       </c>
@@ -14295,7 +14297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A204" s="4" t="s">
         <v>919</v>
       </c>
@@ -14348,7 +14350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A205" s="4" t="s">
         <v>919</v>
       </c>
@@ -14401,7 +14403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A206" s="4" t="s">
         <v>919</v>
       </c>
@@ -14454,7 +14456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A207" s="4" t="s">
         <v>919</v>
       </c>
@@ -14507,7 +14509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A208" s="4" t="s">
         <v>919</v>
       </c>
@@ -14560,7 +14562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A209" s="4" t="s">
         <v>919</v>
       </c>
@@ -14613,7 +14615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A210" s="4" t="s">
         <v>919</v>
       </c>
@@ -14666,7 +14668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A211" s="4" t="s">
         <v>919</v>
       </c>
@@ -14719,7 +14721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A212" s="4" t="s">
         <v>919</v>
       </c>
@@ -14772,7 +14774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A213" s="4" t="s">
         <v>919</v>
       </c>
@@ -14825,7 +14827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A214" s="4" t="s">
         <v>919</v>
       </c>
@@ -14878,7 +14880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A215" s="4" t="s">
         <v>919</v>
       </c>
@@ -14931,7 +14933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A216" s="4" t="s">
         <v>919</v>
       </c>
@@ -14984,7 +14986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A217" s="4" t="s">
         <v>919</v>
       </c>
@@ -15037,7 +15039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A218" s="4" t="s">
         <v>919</v>
       </c>
@@ -15090,7 +15092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A219" s="4" t="s">
         <v>919</v>
       </c>
@@ -15143,7 +15145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A220" s="4" t="s">
         <v>919</v>
       </c>
@@ -15196,7 +15198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A221" s="4" t="s">
         <v>919</v>
       </c>
@@ -15249,7 +15251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A222" s="4" t="s">
         <v>919</v>
       </c>
@@ -15302,7 +15304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A223" s="4" t="s">
         <v>919</v>
       </c>
@@ -15355,7 +15357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A224" s="4" t="s">
         <v>919</v>
       </c>
@@ -15408,7 +15410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A225" s="4" t="s">
         <v>919</v>
       </c>
@@ -15461,7 +15463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A226" s="4" t="s">
         <v>919</v>
       </c>
@@ -15514,7 +15516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A227" s="4" t="s">
         <v>919</v>
       </c>
@@ -15567,7 +15569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A228" s="4" t="s">
         <v>919</v>
       </c>
@@ -15620,7 +15622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A229" s="4" t="s">
         <v>919</v>
       </c>
@@ -15673,7 +15675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A230" s="4" t="s">
         <v>919</v>
       </c>
@@ -15726,7 +15728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A231" s="4" t="s">
         <v>919</v>
       </c>
@@ -15779,7 +15781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A232" s="4" t="s">
         <v>919</v>
       </c>
@@ -15832,7 +15834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A233" s="4" t="s">
         <v>919</v>
       </c>
@@ -15885,7 +15887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A234" s="4" t="s">
         <v>919</v>
       </c>
@@ -15938,7 +15940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A235" s="4" t="s">
         <v>919</v>
       </c>
@@ -15991,7 +15993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A236" s="4" t="s">
         <v>919</v>
       </c>
@@ -16044,7 +16046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A237" s="4" t="s">
         <v>919</v>
       </c>
@@ -16097,7 +16099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A238" s="4" t="s">
         <v>919</v>
       </c>
@@ -16150,7 +16152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A239" s="4" t="s">
         <v>919</v>
       </c>
@@ -16203,7 +16205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A240" s="4" t="s">
         <v>919</v>
       </c>
@@ -16256,7 +16258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A241" s="4" t="s">
         <v>919</v>
       </c>
@@ -16309,7 +16311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A242" s="4" t="s">
         <v>919</v>
       </c>
@@ -16362,7 +16364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A243" s="4" t="s">
         <v>919</v>
       </c>
@@ -16415,7 +16417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A244" s="4" t="s">
         <v>919</v>
       </c>
@@ -16468,7 +16470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A245" s="4" t="s">
         <v>919</v>
       </c>
@@ -16521,7 +16523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A246" s="4" t="s">
         <v>919</v>
       </c>
@@ -16574,7 +16576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A247" s="4" t="s">
         <v>919</v>
       </c>
@@ -16627,7 +16629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A248" s="4" t="s">
         <v>919</v>
       </c>
@@ -16680,7 +16682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A249" s="4" t="s">
         <v>919</v>
       </c>
@@ -16733,7 +16735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A250" s="4" t="s">
         <v>919</v>
       </c>
@@ -16786,7 +16788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="251" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A251" s="4" t="s">
         <v>919</v>
       </c>
@@ -16839,7 +16841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A252" s="4" t="s">
         <v>48</v>
       </c>
@@ -16892,7 +16894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A253" s="4" t="s">
         <v>48</v>
       </c>
@@ -16945,7 +16947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A254" s="4" t="s">
         <v>48</v>
       </c>
@@ -16998,7 +17000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A255" s="4" t="s">
         <v>48</v>
       </c>
@@ -17051,7 +17053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A256" s="4" t="s">
         <v>48</v>
       </c>
@@ -17104,7 +17106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A257" s="4" t="s">
         <v>48</v>
       </c>
@@ -17157,7 +17159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="258" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A258" s="4" t="s">
         <v>48</v>
       </c>
@@ -17210,7 +17212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="259" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A259" s="4" t="s">
         <v>48</v>
       </c>
@@ -17263,7 +17265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="260" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A260" s="4" t="s">
         <v>48</v>
       </c>
@@ -17316,7 +17318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A261" s="4" t="s">
         <v>48</v>
       </c>
@@ -17369,7 +17371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A262" s="4" t="s">
         <v>48</v>
       </c>
@@ -17422,7 +17424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A263" s="4" t="s">
         <v>48</v>
       </c>
@@ -17475,7 +17477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A264" s="4" t="s">
         <v>48</v>
       </c>
@@ -17528,7 +17530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="265" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A265" s="4" t="s">
         <v>48</v>
       </c>
@@ -17581,7 +17583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A266" s="4" t="s">
         <v>48</v>
       </c>
@@ -17634,7 +17636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A267" s="4" t="s">
         <v>48</v>
       </c>
@@ -17687,7 +17689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A268" s="4" t="s">
         <v>48</v>
       </c>
@@ -17740,7 +17742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A269" s="4" t="s">
         <v>48</v>
       </c>
@@ -17793,7 +17795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A270" s="4" t="s">
         <v>48</v>
       </c>
@@ -17846,7 +17848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A271" s="4" t="s">
         <v>48</v>
       </c>
@@ -17899,7 +17901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A272" s="4" t="s">
         <v>48</v>
       </c>
@@ -17952,7 +17954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A273" s="4" t="s">
         <v>48</v>
       </c>
@@ -18005,7 +18007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A274" s="4" t="s">
         <v>48</v>
       </c>
@@ -18058,7 +18060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A275" s="4" t="s">
         <v>48</v>
       </c>
@@ -18111,7 +18113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A276" s="4" t="s">
         <v>48</v>
       </c>
@@ -18164,7 +18166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A277" s="4" t="s">
         <v>48</v>
       </c>
@@ -18217,7 +18219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="278" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A278" s="4" t="s">
         <v>48</v>
       </c>
@@ -18270,7 +18272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A279" s="4" t="s">
         <v>48</v>
       </c>
@@ -18323,7 +18325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A280" s="4" t="s">
         <v>48</v>
       </c>
@@ -18376,7 +18378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="281" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A281" s="4" t="s">
         <v>48</v>
       </c>
@@ -18429,7 +18431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="282" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A282" s="4" t="s">
         <v>48</v>
       </c>
@@ -18482,7 +18484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="283" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A283" s="4" t="s">
         <v>48</v>
       </c>
@@ -18535,7 +18537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A284" s="4" t="s">
         <v>48</v>
       </c>
@@ -18588,7 +18590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A285" s="4" t="s">
         <v>48</v>
       </c>
@@ -18641,7 +18643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A286" s="4" t="s">
         <v>48</v>
       </c>
@@ -18694,7 +18696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="287" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A287" s="4" t="s">
         <v>48</v>
       </c>
@@ -18747,7 +18749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A288" s="12" t="s">
         <v>48</v>
       </c>
@@ -18800,7 +18802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A289" s="12" t="s">
         <v>48</v>
       </c>
@@ -18853,7 +18855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A290" s="12" t="s">
         <v>48</v>
       </c>
@@ -18906,7 +18908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.6">
+    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="A291" s="12" t="s">
         <v>48</v>
       </c>
@@ -18960,7 +18962,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q287" xr:uid="{D4BEF8C4-3AAC-49A4-B2D4-DA4E2DCAF1C2}"/>
+  <autoFilter ref="A1:Q291" xr:uid="{D4BEF8C4-3AAC-49A4-B2D4-DA4E2DCAF1C2}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="ตาพระยา"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState ref="A2:C287">
     <sortCondition ref="C2:C287"/>
   </sortState>
@@ -19099,8 +19107,8 @@
         <v>6.25</v>
       </c>
       <c r="P2" s="30">
-        <f>SUM(E2:O2)</f>
-        <v>12.5</v>
+        <f>SUM(E2:N2)</f>
+        <v>6.25</v>
       </c>
       <c r="Q2" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B2,Dangerous!$N:$N)</f>
@@ -19112,7 +19120,7 @@
       </c>
       <c r="S2" s="31">
         <f>SUM(P2:R2)</f>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.6">
@@ -19156,8 +19164,8 @@
         <v>6.25</v>
       </c>
       <c r="P3" s="30">
-        <f t="shared" ref="P3:P66" si="0">SUM(E3:O3)</f>
-        <v>12.5</v>
+        <f t="shared" ref="P3:P66" si="0">SUM(E3:N3)</f>
+        <v>6.25</v>
       </c>
       <c r="Q3" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B3,Dangerous!$N:$N)</f>
@@ -19169,7 +19177,7 @@
       </c>
       <c r="S3" s="31">
         <f t="shared" ref="S3:S66" si="1">SUM(P3:R3)</f>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.6">
@@ -19214,7 +19222,7 @@
       </c>
       <c r="P4" s="30">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B4,Dangerous!$N:$N)</f>
@@ -19226,7 +19234,7 @@
       </c>
       <c r="S4" s="31">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.6">
@@ -19271,7 +19279,7 @@
       </c>
       <c r="P5" s="30">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q5" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B5,Dangerous!$N:$N)</f>
@@ -19283,7 +19291,7 @@
       </c>
       <c r="S5" s="31">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.6">
@@ -19328,7 +19336,7 @@
       </c>
       <c r="P6" s="30">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q6" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B6,Dangerous!$N:$N)</f>
@@ -19340,7 +19348,7 @@
       </c>
       <c r="S6" s="31">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.6">
@@ -19385,7 +19393,7 @@
       </c>
       <c r="P7" s="30">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q7" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B7,Dangerous!$N:$N)</f>
@@ -19397,7 +19405,7 @@
       </c>
       <c r="S7" s="31">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.6">
@@ -19442,7 +19450,7 @@
       </c>
       <c r="P8" s="30">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B8,Dangerous!$N:$N)</f>
@@ -19454,7 +19462,7 @@
       </c>
       <c r="S8" s="31">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.6">
@@ -19499,7 +19507,7 @@
       </c>
       <c r="P9" s="30">
         <f t="shared" si="0"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q9" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B9,Dangerous!$N:$N)</f>
@@ -19511,7 +19519,7 @@
       </c>
       <c r="S9" s="31">
         <f t="shared" si="1"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.6">
@@ -19556,7 +19564,7 @@
       </c>
       <c r="P10" s="30">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B10,Dangerous!$N:$N)</f>
@@ -19568,7 +19576,7 @@
       </c>
       <c r="S10" s="31">
         <f t="shared" si="1"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.6">
@@ -19613,7 +19621,7 @@
       </c>
       <c r="P11" s="30">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q11" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B11,Dangerous!$N:$N)</f>
@@ -19625,7 +19633,7 @@
       </c>
       <c r="S11" s="31">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.6">
@@ -19670,7 +19678,7 @@
       </c>
       <c r="P12" s="30">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B12,Dangerous!$N:$N)</f>
@@ -19682,7 +19690,7 @@
       </c>
       <c r="S12" s="31">
         <f t="shared" si="1"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.6">
@@ -19784,7 +19792,7 @@
       </c>
       <c r="P14" s="30">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q14" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B14,Dangerous!$N:$N)</f>
@@ -19796,7 +19804,7 @@
       </c>
       <c r="S14" s="31">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.6">
@@ -19898,7 +19906,7 @@
       </c>
       <c r="P16" s="30">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q16" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B16,Dangerous!$N:$N)</f>
@@ -19910,7 +19918,7 @@
       </c>
       <c r="S16" s="31">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.6">
@@ -19955,7 +19963,7 @@
       </c>
       <c r="P17" s="30">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q17" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B17,Dangerous!$N:$N)</f>
@@ -19967,7 +19975,7 @@
       </c>
       <c r="S17" s="31">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.6">
@@ -20012,7 +20020,7 @@
       </c>
       <c r="P18" s="30">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q18" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B18,Dangerous!$N:$N)</f>
@@ -20024,7 +20032,7 @@
       </c>
       <c r="S18" s="31">
         <f t="shared" si="1"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.6">
@@ -20069,7 +20077,7 @@
       </c>
       <c r="P19" s="30">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q19" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B19,Dangerous!$N:$N)</f>
@@ -20081,7 +20089,7 @@
       </c>
       <c r="S19" s="31">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.6">
@@ -20126,7 +20134,7 @@
       </c>
       <c r="P20" s="30">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q20" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B20,Dangerous!$N:$N)</f>
@@ -20138,7 +20146,7 @@
       </c>
       <c r="S20" s="31">
         <f t="shared" si="1"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.6">
@@ -20240,7 +20248,7 @@
       </c>
       <c r="P22" s="30">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q22" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B22,Dangerous!$N:$N)</f>
@@ -20252,7 +20260,7 @@
       </c>
       <c r="S22" s="31">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.6">
@@ -20297,7 +20305,7 @@
       </c>
       <c r="P23" s="30">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B23,Dangerous!$N:$N)</f>
@@ -20309,7 +20317,7 @@
       </c>
       <c r="S23" s="31">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.6">
@@ -20354,7 +20362,7 @@
       </c>
       <c r="P24" s="30">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q24" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B24,Dangerous!$N:$N)</f>
@@ -20366,7 +20374,7 @@
       </c>
       <c r="S24" s="31">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.6">
@@ -20411,7 +20419,7 @@
       </c>
       <c r="P25" s="30">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B25,Dangerous!$N:$N)</f>
@@ -20423,7 +20431,7 @@
       </c>
       <c r="S25" s="31">
         <f t="shared" si="1"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.6">
@@ -20468,7 +20476,7 @@
       </c>
       <c r="P26" s="30">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q26" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B26,Dangerous!$N:$N)</f>
@@ -20480,7 +20488,7 @@
       </c>
       <c r="S26" s="31">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.6">
@@ -20525,7 +20533,7 @@
       </c>
       <c r="P27" s="30">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q27" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B27,Dangerous!$N:$N)</f>
@@ -20537,7 +20545,7 @@
       </c>
       <c r="S27" s="31">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.6">
@@ -20582,7 +20590,7 @@
       </c>
       <c r="P28" s="30">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q28" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B28,Dangerous!$N:$N)</f>
@@ -20594,7 +20602,7 @@
       </c>
       <c r="S28" s="31">
         <f t="shared" si="1"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.6">
@@ -20639,7 +20647,7 @@
       </c>
       <c r="P29" s="30">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q29" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B29,Dangerous!$N:$N)</f>
@@ -20651,7 +20659,7 @@
       </c>
       <c r="S29" s="31">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.6">
@@ -20696,7 +20704,7 @@
       </c>
       <c r="P30" s="30">
         <f t="shared" si="0"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q30" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B30,Dangerous!$N:$N)</f>
@@ -20708,7 +20716,7 @@
       </c>
       <c r="S30" s="31">
         <f t="shared" si="1"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.6">
@@ -20753,7 +20761,7 @@
       </c>
       <c r="P31" s="30">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q31" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B31,Dangerous!$N:$N)</f>
@@ -20765,7 +20773,7 @@
       </c>
       <c r="S31" s="31">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.6">
@@ -20810,7 +20818,7 @@
       </c>
       <c r="P32" s="30">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q32" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B32,Dangerous!$N:$N)</f>
@@ -20822,7 +20830,7 @@
       </c>
       <c r="S32" s="31">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.6">
@@ -20867,7 +20875,7 @@
       </c>
       <c r="P33" s="30">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q33" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B33,Dangerous!$N:$N)</f>
@@ -20879,7 +20887,7 @@
       </c>
       <c r="S33" s="31">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.6">
@@ -20924,7 +20932,7 @@
       </c>
       <c r="P34" s="30">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q34" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B34,Dangerous!$N:$N)</f>
@@ -20936,7 +20944,7 @@
       </c>
       <c r="S34" s="31">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.6">
@@ -20981,7 +20989,7 @@
       </c>
       <c r="P35" s="30">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q35" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B35,Dangerous!$N:$N)</f>
@@ -20993,7 +21001,7 @@
       </c>
       <c r="S35" s="31">
         <f t="shared" si="1"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.6">
@@ -21038,7 +21046,7 @@
       </c>
       <c r="P36" s="30">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q36" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B36,Dangerous!$N:$N)</f>
@@ -21050,7 +21058,7 @@
       </c>
       <c r="S36" s="31">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.6">
@@ -21152,7 +21160,7 @@
       </c>
       <c r="P38" s="30">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q38" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B38,Dangerous!$N:$N)</f>
@@ -21164,7 +21172,7 @@
       </c>
       <c r="S38" s="31">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.6">
@@ -21323,7 +21331,7 @@
       </c>
       <c r="P41" s="30">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q41" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B41,Dangerous!$N:$N)</f>
@@ -21335,7 +21343,7 @@
       </c>
       <c r="S41" s="31">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.6">
@@ -21380,7 +21388,7 @@
       </c>
       <c r="P42" s="30">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q42" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B42,Dangerous!$N:$N)</f>
@@ -21392,7 +21400,7 @@
       </c>
       <c r="S42" s="31">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.6">
@@ -21608,7 +21616,7 @@
       </c>
       <c r="P46" s="30">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q46" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B46,Dangerous!$N:$N)</f>
@@ -21620,7 +21628,7 @@
       </c>
       <c r="S46" s="31">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.6">
@@ -21665,7 +21673,7 @@
       </c>
       <c r="P47" s="30">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q47" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B47,Dangerous!$N:$N)</f>
@@ -21677,7 +21685,7 @@
       </c>
       <c r="S47" s="31">
         <f t="shared" si="1"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.6">
@@ -21722,7 +21730,7 @@
       </c>
       <c r="P48" s="30">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q48" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B48,Dangerous!$N:$N)</f>
@@ -21734,7 +21742,7 @@
       </c>
       <c r="S48" s="31">
         <f t="shared" si="1"/>
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.6">
@@ -21779,7 +21787,7 @@
       </c>
       <c r="P49" s="30">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q49" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B49,Dangerous!$N:$N)</f>
@@ -21791,7 +21799,7 @@
       </c>
       <c r="S49" s="31">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.6">
@@ -21836,7 +21844,7 @@
       </c>
       <c r="P50" s="30">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q50" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B50,Dangerous!$N:$N)</f>
@@ -21848,7 +21856,7 @@
       </c>
       <c r="S50" s="31">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.6">
@@ -21893,7 +21901,7 @@
       </c>
       <c r="P51" s="30">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q51" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B51,Dangerous!$N:$N)</f>
@@ -21905,7 +21913,7 @@
       </c>
       <c r="S51" s="31">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.6">
@@ -22007,7 +22015,7 @@
       </c>
       <c r="P53" s="30">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q53" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B53,Dangerous!$N:$N)</f>
@@ -22019,7 +22027,7 @@
       </c>
       <c r="S53" s="31">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.6">
@@ -22064,7 +22072,7 @@
       </c>
       <c r="P54" s="30">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q54" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B54,Dangerous!$N:$N)</f>
@@ -22076,7 +22084,7 @@
       </c>
       <c r="S54" s="31">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.6">
@@ -22121,7 +22129,7 @@
       </c>
       <c r="P55" s="30">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q55" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B55,Dangerous!$N:$N)</f>
@@ -22133,7 +22141,7 @@
       </c>
       <c r="S55" s="31">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.6">
@@ -22178,7 +22186,7 @@
       </c>
       <c r="P56" s="30">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q56" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B56,Dangerous!$N:$N)</f>
@@ -22190,7 +22198,7 @@
       </c>
       <c r="S56" s="31">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.6">
@@ -22235,7 +22243,7 @@
       </c>
       <c r="P57" s="30">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q57" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B57,Dangerous!$N:$N)</f>
@@ -22247,7 +22255,7 @@
       </c>
       <c r="S57" s="31">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.6">
@@ -22292,7 +22300,7 @@
       </c>
       <c r="P58" s="30">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q58" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B58,Dangerous!$N:$N)</f>
@@ -22304,7 +22312,7 @@
       </c>
       <c r="S58" s="31">
         <f t="shared" si="1"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.6">
@@ -22406,7 +22414,7 @@
       </c>
       <c r="P60" s="30">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q60" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B60,Dangerous!$N:$N)</f>
@@ -22418,7 +22426,7 @@
       </c>
       <c r="S60" s="31">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.6">
@@ -22463,7 +22471,7 @@
       </c>
       <c r="P61" s="30">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q61" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B61,Dangerous!$N:$N)</f>
@@ -22475,7 +22483,7 @@
       </c>
       <c r="S61" s="31">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.6">
@@ -22577,7 +22585,7 @@
       </c>
       <c r="P63" s="30">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q63" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B63,Dangerous!$N:$N)</f>
@@ -22589,7 +22597,7 @@
       </c>
       <c r="S63" s="31">
         <f t="shared" si="1"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.6">
@@ -22691,7 +22699,7 @@
       </c>
       <c r="P65" s="30">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q65" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B65,Dangerous!$N:$N)</f>
@@ -22703,7 +22711,7 @@
       </c>
       <c r="S65" s="31">
         <f t="shared" si="1"/>
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.6">
@@ -22748,7 +22756,7 @@
       </c>
       <c r="P66" s="30">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q66" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B66,Dangerous!$N:$N)</f>
@@ -22760,7 +22768,7 @@
       </c>
       <c r="S66" s="31">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.6">
@@ -22804,8 +22812,8 @@
         <v>6.25</v>
       </c>
       <c r="P67" s="30">
-        <f t="shared" ref="P67:P130" si="2">SUM(E67:O67)</f>
-        <v>12.5</v>
+        <f t="shared" ref="P67:P130" si="2">SUM(E67:N67)</f>
+        <v>6.25</v>
       </c>
       <c r="Q67" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B67,Dangerous!$N:$N)</f>
@@ -22817,7 +22825,7 @@
       </c>
       <c r="S67" s="31">
         <f t="shared" ref="S67:S130" si="3">SUM(P67:R67)</f>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.6">
@@ -22862,7 +22870,7 @@
       </c>
       <c r="P68" s="30">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q68" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B68,Dangerous!$N:$N)</f>
@@ -22874,7 +22882,7 @@
       </c>
       <c r="S68" s="31">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.6">
@@ -22919,7 +22927,7 @@
       </c>
       <c r="P69" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q69" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B69,Dangerous!$N:$N)</f>
@@ -22931,7 +22939,7 @@
       </c>
       <c r="S69" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.6">
@@ -22976,7 +22984,7 @@
       </c>
       <c r="P70" s="30">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q70" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B70,Dangerous!$N:$N)</f>
@@ -22988,7 +22996,7 @@
       </c>
       <c r="S70" s="31">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.6">
@@ -23033,7 +23041,7 @@
       </c>
       <c r="P71" s="30">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q71" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B71,Dangerous!$N:$N)</f>
@@ -23045,7 +23053,7 @@
       </c>
       <c r="S71" s="31">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.6">
@@ -23090,7 +23098,7 @@
       </c>
       <c r="P72" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q72" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B72,Dangerous!$N:$N)</f>
@@ -23102,7 +23110,7 @@
       </c>
       <c r="S72" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.6">
@@ -23147,7 +23155,7 @@
       </c>
       <c r="P73" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q73" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B73,Dangerous!$N:$N)</f>
@@ -23159,7 +23167,7 @@
       </c>
       <c r="S73" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.6">
@@ -23204,7 +23212,7 @@
       </c>
       <c r="P74" s="30">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q74" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B74,Dangerous!$N:$N)</f>
@@ -23216,7 +23224,7 @@
       </c>
       <c r="S74" s="31">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.6">
@@ -23261,7 +23269,7 @@
       </c>
       <c r="P75" s="30">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q75" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B75,Dangerous!$N:$N)</f>
@@ -23273,7 +23281,7 @@
       </c>
       <c r="S75" s="31">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.6">
@@ -23318,7 +23326,7 @@
       </c>
       <c r="P76" s="30">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q76" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B76,Dangerous!$N:$N)</f>
@@ -23330,7 +23338,7 @@
       </c>
       <c r="S76" s="31">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.6">
@@ -23375,7 +23383,7 @@
       </c>
       <c r="P77" s="30">
         <f t="shared" si="2"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q77" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B77,Dangerous!$N:$N)</f>
@@ -23387,7 +23395,7 @@
       </c>
       <c r="S77" s="31">
         <f t="shared" si="3"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.6">
@@ -23432,7 +23440,7 @@
       </c>
       <c r="P78" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q78" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B78,Dangerous!$N:$N)</f>
@@ -23444,7 +23452,7 @@
       </c>
       <c r="S78" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.6">
@@ -23489,7 +23497,7 @@
       </c>
       <c r="P79" s="30">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q79" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B79,Dangerous!$N:$N)</f>
@@ -23501,7 +23509,7 @@
       </c>
       <c r="S79" s="31">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.6">
@@ -23546,7 +23554,7 @@
       </c>
       <c r="P80" s="30">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q80" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B80,Dangerous!$N:$N)</f>
@@ -23558,7 +23566,7 @@
       </c>
       <c r="S80" s="31">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.6">
@@ -23603,7 +23611,7 @@
       </c>
       <c r="P81" s="30">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q81" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B81,Dangerous!$N:$N)</f>
@@ -23615,7 +23623,7 @@
       </c>
       <c r="S81" s="31">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.6">
@@ -23660,7 +23668,7 @@
       </c>
       <c r="P82" s="30">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q82" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B82,Dangerous!$N:$N)</f>
@@ -23672,7 +23680,7 @@
       </c>
       <c r="S82" s="31">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.6">
@@ -23717,7 +23725,7 @@
       </c>
       <c r="P83" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q83" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B83,Dangerous!$N:$N)</f>
@@ -23729,7 +23737,7 @@
       </c>
       <c r="S83" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.6">
@@ -23774,7 +23782,7 @@
       </c>
       <c r="P84" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q84" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B84,Dangerous!$N:$N)</f>
@@ -23786,7 +23794,7 @@
       </c>
       <c r="S84" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.6">
@@ -23831,7 +23839,7 @@
       </c>
       <c r="P85" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q85" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B85,Dangerous!$N:$N)</f>
@@ -23843,7 +23851,7 @@
       </c>
       <c r="S85" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.6">
@@ -23888,7 +23896,7 @@
       </c>
       <c r="P86" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q86" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B86,Dangerous!$N:$N)</f>
@@ -23900,7 +23908,7 @@
       </c>
       <c r="S86" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.6">
@@ -23945,7 +23953,7 @@
       </c>
       <c r="P87" s="30">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q87" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B87,Dangerous!$N:$N)</f>
@@ -23957,7 +23965,7 @@
       </c>
       <c r="S87" s="31">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.6">
@@ -24002,7 +24010,7 @@
       </c>
       <c r="P88" s="30">
         <f t="shared" si="2"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q88" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B88,Dangerous!$N:$N)</f>
@@ -24014,7 +24022,7 @@
       </c>
       <c r="S88" s="31">
         <f t="shared" si="3"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.6">
@@ -24059,7 +24067,7 @@
       </c>
       <c r="P89" s="30">
         <f t="shared" si="2"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q89" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B89,Dangerous!$N:$N)</f>
@@ -24071,7 +24079,7 @@
       </c>
       <c r="S89" s="31">
         <f t="shared" si="3"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.6">
@@ -24116,7 +24124,7 @@
       </c>
       <c r="P90" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q90" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B90,Dangerous!$N:$N)</f>
@@ -24128,7 +24136,7 @@
       </c>
       <c r="S90" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.6">
@@ -24173,7 +24181,7 @@
       </c>
       <c r="P91" s="30">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q91" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B91,Dangerous!$N:$N)</f>
@@ -24185,7 +24193,7 @@
       </c>
       <c r="S91" s="31">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.6">
@@ -24230,7 +24238,7 @@
       </c>
       <c r="P92" s="30">
         <f t="shared" si="2"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q92" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B92,Dangerous!$N:$N)</f>
@@ -24242,7 +24250,7 @@
       </c>
       <c r="S92" s="31">
         <f t="shared" si="3"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.6">
@@ -24287,7 +24295,7 @@
       </c>
       <c r="P93" s="30">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q93" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B93,Dangerous!$N:$N)</f>
@@ -24299,7 +24307,7 @@
       </c>
       <c r="S93" s="31">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.6">
@@ -24344,7 +24352,7 @@
       </c>
       <c r="P94" s="30">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q94" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B94,Dangerous!$N:$N)</f>
@@ -24356,7 +24364,7 @@
       </c>
       <c r="S94" s="31">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.6">
@@ -24401,7 +24409,7 @@
       </c>
       <c r="P95" s="30">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q95" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B95,Dangerous!$N:$N)</f>
@@ -24413,7 +24421,7 @@
       </c>
       <c r="S95" s="31">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.6">
@@ -24458,7 +24466,7 @@
       </c>
       <c r="P96" s="30">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q96" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B96,Dangerous!$N:$N)</f>
@@ -24470,7 +24478,7 @@
       </c>
       <c r="S96" s="31">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.6">
@@ -24515,7 +24523,7 @@
       </c>
       <c r="P97" s="30">
         <f t="shared" si="2"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q97" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B97,Dangerous!$N:$N)</f>
@@ -24527,7 +24535,7 @@
       </c>
       <c r="S97" s="31">
         <f t="shared" si="3"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.6">
@@ -24572,7 +24580,7 @@
       </c>
       <c r="P98" s="30">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q98" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B98,Dangerous!$N:$N)</f>
@@ -24584,7 +24592,7 @@
       </c>
       <c r="S98" s="31">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.6">
@@ -24629,7 +24637,7 @@
       </c>
       <c r="P99" s="30">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q99" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B99,Dangerous!$N:$N)</f>
@@ -24641,7 +24649,7 @@
       </c>
       <c r="S99" s="31">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.6">
@@ -24686,7 +24694,7 @@
       </c>
       <c r="P100" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q100" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B100,Dangerous!$N:$N)</f>
@@ -24698,7 +24706,7 @@
       </c>
       <c r="S100" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.6">
@@ -24743,7 +24751,7 @@
       </c>
       <c r="P101" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q101" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B101,Dangerous!$N:$N)</f>
@@ -24755,7 +24763,7 @@
       </c>
       <c r="S101" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.6">
@@ -24800,7 +24808,7 @@
       </c>
       <c r="P102" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q102" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B102,Dangerous!$N:$N)</f>
@@ -24812,7 +24820,7 @@
       </c>
       <c r="S102" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.6">
@@ -24857,7 +24865,7 @@
       </c>
       <c r="P103" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q103" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B103,Dangerous!$N:$N)</f>
@@ -24869,7 +24877,7 @@
       </c>
       <c r="S103" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.6">
@@ -24914,7 +24922,7 @@
       </c>
       <c r="P104" s="30">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q104" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B104,Dangerous!$N:$N)</f>
@@ -24926,7 +24934,7 @@
       </c>
       <c r="S104" s="31">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.6">
@@ -24971,7 +24979,7 @@
       </c>
       <c r="P105" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q105" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B105,Dangerous!$N:$N)</f>
@@ -24983,7 +24991,7 @@
       </c>
       <c r="S105" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.6">
@@ -25028,7 +25036,7 @@
       </c>
       <c r="P106" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q106" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B106,Dangerous!$N:$N)</f>
@@ -25040,7 +25048,7 @@
       </c>
       <c r="S106" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.6">
@@ -25085,7 +25093,7 @@
       </c>
       <c r="P107" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q107" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B107,Dangerous!$N:$N)</f>
@@ -25097,7 +25105,7 @@
       </c>
       <c r="S107" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.6">
@@ -25142,7 +25150,7 @@
       </c>
       <c r="P108" s="30">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q108" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B108,Dangerous!$N:$N)</f>
@@ -25154,7 +25162,7 @@
       </c>
       <c r="S108" s="31">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.6">
@@ -25199,7 +25207,7 @@
       </c>
       <c r="P109" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q109" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B109,Dangerous!$N:$N)</f>
@@ -25211,7 +25219,7 @@
       </c>
       <c r="S109" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.6">
@@ -25313,7 +25321,7 @@
       </c>
       <c r="P111" s="30">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q111" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B111,Dangerous!$N:$N)</f>
@@ -25325,7 +25333,7 @@
       </c>
       <c r="S111" s="31">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.6">
@@ -25370,7 +25378,7 @@
       </c>
       <c r="P112" s="30">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q112" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B112,Dangerous!$N:$N)</f>
@@ -25382,7 +25390,7 @@
       </c>
       <c r="S112" s="31">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.6">
@@ -25427,7 +25435,7 @@
       </c>
       <c r="P113" s="30">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q113" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B113,Dangerous!$N:$N)</f>
@@ -25439,7 +25447,7 @@
       </c>
       <c r="S113" s="31">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.6">
@@ -25484,7 +25492,7 @@
       </c>
       <c r="P114" s="30">
         <f t="shared" si="2"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q114" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B114,Dangerous!$N:$N)</f>
@@ -25496,7 +25504,7 @@
       </c>
       <c r="S114" s="31">
         <f t="shared" si="3"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.6">
@@ -25541,7 +25549,7 @@
       </c>
       <c r="P115" s="30">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q115" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B115,Dangerous!$N:$N)</f>
@@ -25553,7 +25561,7 @@
       </c>
       <c r="S115" s="31">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.6">
@@ -25598,7 +25606,7 @@
       </c>
       <c r="P116" s="30">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q116" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B116,Dangerous!$N:$N)</f>
@@ -25610,7 +25618,7 @@
       </c>
       <c r="S116" s="31">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.6">
@@ -25655,7 +25663,7 @@
       </c>
       <c r="P117" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q117" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B117,Dangerous!$N:$N)</f>
@@ -25667,7 +25675,7 @@
       </c>
       <c r="S117" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.6">
@@ -25712,7 +25720,7 @@
       </c>
       <c r="P118" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q118" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B118,Dangerous!$N:$N)</f>
@@ -25724,7 +25732,7 @@
       </c>
       <c r="S118" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.6">
@@ -25769,7 +25777,7 @@
       </c>
       <c r="P119" s="30">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q119" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B119,Dangerous!$N:$N)</f>
@@ -25781,7 +25789,7 @@
       </c>
       <c r="S119" s="31">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.6">
@@ -25826,7 +25834,7 @@
       </c>
       <c r="P120" s="30">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q120" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B120,Dangerous!$N:$N)</f>
@@ -25838,7 +25846,7 @@
       </c>
       <c r="S120" s="31">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.6">
@@ -25883,7 +25891,7 @@
       </c>
       <c r="P121" s="30">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q121" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B121,Dangerous!$N:$N)</f>
@@ -25895,7 +25903,7 @@
       </c>
       <c r="S121" s="31">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.6">
@@ -25940,7 +25948,7 @@
       </c>
       <c r="P122" s="30">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q122" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B122,Dangerous!$N:$N)</f>
@@ -25952,7 +25960,7 @@
       </c>
       <c r="S122" s="31">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.6">
@@ -25997,7 +26005,7 @@
       </c>
       <c r="P123" s="30">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q123" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B123,Dangerous!$N:$N)</f>
@@ -26009,7 +26017,7 @@
       </c>
       <c r="S123" s="31">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.6">
@@ -26054,7 +26062,7 @@
       </c>
       <c r="P124" s="30">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q124" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B124,Dangerous!$N:$N)</f>
@@ -26066,7 +26074,7 @@
       </c>
       <c r="S124" s="31">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.6">
@@ -26168,7 +26176,7 @@
       </c>
       <c r="P126" s="30">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q126" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B126,Dangerous!$N:$N)</f>
@@ -26180,7 +26188,7 @@
       </c>
       <c r="S126" s="31">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.6">
@@ -26225,7 +26233,7 @@
       </c>
       <c r="P127" s="30">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q127" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B127,Dangerous!$N:$N)</f>
@@ -26237,7 +26245,7 @@
       </c>
       <c r="S127" s="31">
         <f t="shared" si="3"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.6">
@@ -26282,7 +26290,7 @@
       </c>
       <c r="P128" s="30">
         <f t="shared" si="2"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q128" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B128,Dangerous!$N:$N)</f>
@@ -26294,7 +26302,7 @@
       </c>
       <c r="S128" s="31">
         <f t="shared" si="3"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="129" spans="1:19" x14ac:dyDescent="0.6">
@@ -26339,7 +26347,7 @@
       </c>
       <c r="P129" s="30">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q129" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B129,Dangerous!$N:$N)</f>
@@ -26351,7 +26359,7 @@
       </c>
       <c r="S129" s="31">
         <f t="shared" si="3"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="130" spans="1:19" x14ac:dyDescent="0.6">
@@ -26396,7 +26404,7 @@
       </c>
       <c r="P130" s="30">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q130" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B130,Dangerous!$N:$N)</f>
@@ -26408,7 +26416,7 @@
       </c>
       <c r="S130" s="31">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.6">
@@ -26452,8 +26460,8 @@
         <v>5</v>
       </c>
       <c r="P131" s="30">
-        <f t="shared" ref="P131:P194" si="4">SUM(E131:O131)</f>
-        <v>10</v>
+        <f t="shared" ref="P131:P194" si="4">SUM(E131:N131)</f>
+        <v>5</v>
       </c>
       <c r="Q131" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B131,Dangerous!$N:$N)</f>
@@ -26465,7 +26473,7 @@
       </c>
       <c r="S131" s="31">
         <f t="shared" ref="S131:S194" si="5">SUM(P131:R131)</f>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:19" x14ac:dyDescent="0.6">
@@ -26510,7 +26518,7 @@
       </c>
       <c r="P132" s="30">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q132" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B132,Dangerous!$N:$N)</f>
@@ -26522,7 +26530,7 @@
       </c>
       <c r="S132" s="31">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.6">
@@ -26567,7 +26575,7 @@
       </c>
       <c r="P133" s="30">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q133" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B133,Dangerous!$N:$N)</f>
@@ -26579,7 +26587,7 @@
       </c>
       <c r="S133" s="31">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.6">
@@ -26624,7 +26632,7 @@
       </c>
       <c r="P134" s="30">
         <f t="shared" si="4"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q134" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B134,Dangerous!$N:$N)</f>
@@ -26636,7 +26644,7 @@
       </c>
       <c r="S134" s="31">
         <f t="shared" si="5"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="135" spans="1:19" x14ac:dyDescent="0.6">
@@ -26681,7 +26689,7 @@
       </c>
       <c r="P135" s="30">
         <f t="shared" si="4"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q135" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B135,Dangerous!$N:$N)</f>
@@ -26693,7 +26701,7 @@
       </c>
       <c r="S135" s="31">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.6">
@@ -26738,7 +26746,7 @@
       </c>
       <c r="P136" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q136" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B136,Dangerous!$N:$N)</f>
@@ -26750,7 +26758,7 @@
       </c>
       <c r="S136" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="137" spans="1:19" x14ac:dyDescent="0.6">
@@ -26795,7 +26803,7 @@
       </c>
       <c r="P137" s="30">
         <f t="shared" si="4"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q137" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B137,Dangerous!$N:$N)</f>
@@ -26807,7 +26815,7 @@
       </c>
       <c r="S137" s="31">
         <f t="shared" si="5"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.6">
@@ -26852,7 +26860,7 @@
       </c>
       <c r="P138" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q138" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B138,Dangerous!$N:$N)</f>
@@ -26864,7 +26872,7 @@
       </c>
       <c r="S138" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="139" spans="1:19" x14ac:dyDescent="0.6">
@@ -26966,7 +26974,7 @@
       </c>
       <c r="P140" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q140" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B140,Dangerous!$N:$N)</f>
@@ -26978,7 +26986,7 @@
       </c>
       <c r="S140" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="141" spans="1:19" x14ac:dyDescent="0.6">
@@ -27023,7 +27031,7 @@
       </c>
       <c r="P141" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q141" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B141,Dangerous!$N:$N)</f>
@@ -27035,7 +27043,7 @@
       </c>
       <c r="S141" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="142" spans="1:19" x14ac:dyDescent="0.6">
@@ -27080,7 +27088,7 @@
       </c>
       <c r="P142" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q142" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B142,Dangerous!$N:$N)</f>
@@ -27092,7 +27100,7 @@
       </c>
       <c r="S142" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="143" spans="1:19" x14ac:dyDescent="0.6">
@@ -27137,7 +27145,7 @@
       </c>
       <c r="P143" s="30">
         <f t="shared" si="4"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q143" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B143,Dangerous!$N:$N)</f>
@@ -27149,7 +27157,7 @@
       </c>
       <c r="S143" s="31">
         <f t="shared" si="5"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.6">
@@ -27194,7 +27202,7 @@
       </c>
       <c r="P144" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q144" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B144,Dangerous!$N:$N)</f>
@@ -27206,7 +27214,7 @@
       </c>
       <c r="S144" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.6">
@@ -27251,7 +27259,7 @@
       </c>
       <c r="P145" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q145" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B145,Dangerous!$N:$N)</f>
@@ -27263,7 +27271,7 @@
       </c>
       <c r="S145" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="146" spans="1:19" x14ac:dyDescent="0.6">
@@ -27308,7 +27316,7 @@
       </c>
       <c r="P146" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q146" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B146,Dangerous!$N:$N)</f>
@@ -27320,7 +27328,7 @@
       </c>
       <c r="S146" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="147" spans="1:19" x14ac:dyDescent="0.6">
@@ -27365,7 +27373,7 @@
       </c>
       <c r="P147" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q147" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B147,Dangerous!$N:$N)</f>
@@ -27377,7 +27385,7 @@
       </c>
       <c r="S147" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.6">
@@ -27422,7 +27430,7 @@
       </c>
       <c r="P148" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q148" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B148,Dangerous!$N:$N)</f>
@@ -27434,7 +27442,7 @@
       </c>
       <c r="S148" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.6">
@@ -27479,7 +27487,7 @@
       </c>
       <c r="P149" s="30">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q149" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B149,Dangerous!$N:$N)</f>
@@ -27491,7 +27499,7 @@
       </c>
       <c r="S149" s="31">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.6">
@@ -27536,7 +27544,7 @@
       </c>
       <c r="P150" s="30">
         <f t="shared" si="4"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q150" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B150,Dangerous!$N:$N)</f>
@@ -27548,7 +27556,7 @@
       </c>
       <c r="S150" s="31">
         <f t="shared" si="5"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.6">
@@ -27593,7 +27601,7 @@
       </c>
       <c r="P151" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q151" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B151,Dangerous!$N:$N)</f>
@@ -27605,7 +27613,7 @@
       </c>
       <c r="S151" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="152" spans="1:19" x14ac:dyDescent="0.6">
@@ -27707,7 +27715,7 @@
       </c>
       <c r="P153" s="30">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q153" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B153,Dangerous!$N:$N)</f>
@@ -27719,7 +27727,7 @@
       </c>
       <c r="S153" s="31">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:19" x14ac:dyDescent="0.6">
@@ -27764,7 +27772,7 @@
       </c>
       <c r="P154" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q154" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B154,Dangerous!$N:$N)</f>
@@ -27776,7 +27784,7 @@
       </c>
       <c r="S154" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.6">
@@ -27821,7 +27829,7 @@
       </c>
       <c r="P155" s="30">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q155" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B155,Dangerous!$N:$N)</f>
@@ -27833,7 +27841,7 @@
       </c>
       <c r="S155" s="31">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:19" x14ac:dyDescent="0.6">
@@ -27878,7 +27886,7 @@
       </c>
       <c r="P156" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q156" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B156,Dangerous!$N:$N)</f>
@@ -27890,7 +27898,7 @@
       </c>
       <c r="S156" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="157" spans="1:19" x14ac:dyDescent="0.6">
@@ -27935,7 +27943,7 @@
       </c>
       <c r="P157" s="30">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q157" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B157,Dangerous!$N:$N)</f>
@@ -27947,7 +27955,7 @@
       </c>
       <c r="S157" s="31">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="158" spans="1:19" x14ac:dyDescent="0.6">
@@ -27992,7 +28000,7 @@
       </c>
       <c r="P158" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q158" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B158,Dangerous!$N:$N)</f>
@@ -28004,7 +28012,7 @@
       </c>
       <c r="S158" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="159" spans="1:19" x14ac:dyDescent="0.6">
@@ -28049,7 +28057,7 @@
       </c>
       <c r="P159" s="30">
         <f t="shared" si="4"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q159" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B159,Dangerous!$N:$N)</f>
@@ -28061,7 +28069,7 @@
       </c>
       <c r="S159" s="31">
         <f t="shared" si="5"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="160" spans="1:19" x14ac:dyDescent="0.6">
@@ -28106,7 +28114,7 @@
       </c>
       <c r="P160" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q160" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B160,Dangerous!$N:$N)</f>
@@ -28118,7 +28126,7 @@
       </c>
       <c r="S160" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="161" spans="1:19" x14ac:dyDescent="0.6">
@@ -28220,7 +28228,7 @@
       </c>
       <c r="P162" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q162" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B162,Dangerous!$N:$N)</f>
@@ -28232,7 +28240,7 @@
       </c>
       <c r="S162" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="163" spans="1:19" x14ac:dyDescent="0.6">
@@ -28277,7 +28285,7 @@
       </c>
       <c r="P163" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q163" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B163,Dangerous!$N:$N)</f>
@@ -28289,7 +28297,7 @@
       </c>
       <c r="S163" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="164" spans="1:19" x14ac:dyDescent="0.6">
@@ -28334,7 +28342,7 @@
       </c>
       <c r="P164" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q164" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B164,Dangerous!$N:$N)</f>
@@ -28346,7 +28354,7 @@
       </c>
       <c r="S164" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="165" spans="1:19" x14ac:dyDescent="0.6">
@@ -28391,7 +28399,7 @@
       </c>
       <c r="P165" s="30">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q165" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B165,Dangerous!$N:$N)</f>
@@ -28403,7 +28411,7 @@
       </c>
       <c r="S165" s="31">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="166" spans="1:19" x14ac:dyDescent="0.6">
@@ -28448,7 +28456,7 @@
       </c>
       <c r="P166" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q166" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B166,Dangerous!$N:$N)</f>
@@ -28460,7 +28468,7 @@
       </c>
       <c r="S166" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="167" spans="1:19" x14ac:dyDescent="0.6">
@@ -28505,7 +28513,7 @@
       </c>
       <c r="P167" s="30">
         <f t="shared" si="4"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q167" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B167,Dangerous!$N:$N)</f>
@@ -28517,7 +28525,7 @@
       </c>
       <c r="S167" s="31">
         <f t="shared" si="5"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="168" spans="1:19" x14ac:dyDescent="0.6">
@@ -28562,7 +28570,7 @@
       </c>
       <c r="P168" s="30">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q168" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B168,Dangerous!$N:$N)</f>
@@ -28574,7 +28582,7 @@
       </c>
       <c r="S168" s="31">
         <f t="shared" si="5"/>
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:19" x14ac:dyDescent="0.6">
@@ -28676,7 +28684,7 @@
       </c>
       <c r="P170" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q170" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B170,Dangerous!$N:$N)</f>
@@ -28688,7 +28696,7 @@
       </c>
       <c r="S170" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="171" spans="1:19" x14ac:dyDescent="0.6">
@@ -28790,7 +28798,7 @@
       </c>
       <c r="P172" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q172" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B172,Dangerous!$N:$N)</f>
@@ -28802,7 +28810,7 @@
       </c>
       <c r="S172" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="173" spans="1:19" x14ac:dyDescent="0.6">
@@ -28847,7 +28855,7 @@
       </c>
       <c r="P173" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q173" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B173,Dangerous!$N:$N)</f>
@@ -28859,7 +28867,7 @@
       </c>
       <c r="S173" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="174" spans="1:19" x14ac:dyDescent="0.6">
@@ -28904,7 +28912,7 @@
       </c>
       <c r="P174" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q174" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B174,Dangerous!$N:$N)</f>
@@ -28916,7 +28924,7 @@
       </c>
       <c r="S174" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="175" spans="1:19" x14ac:dyDescent="0.6">
@@ -28961,7 +28969,7 @@
       </c>
       <c r="P175" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q175" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B175,Dangerous!$N:$N)</f>
@@ -28973,7 +28981,7 @@
       </c>
       <c r="S175" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="176" spans="1:19" x14ac:dyDescent="0.6">
@@ -29018,7 +29026,7 @@
       </c>
       <c r="P176" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q176" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B176,Dangerous!$N:$N)</f>
@@ -29030,7 +29038,7 @@
       </c>
       <c r="S176" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="177" spans="1:19" x14ac:dyDescent="0.6">
@@ -29075,7 +29083,7 @@
       </c>
       <c r="P177" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q177" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B177,Dangerous!$N:$N)</f>
@@ -29087,7 +29095,7 @@
       </c>
       <c r="S177" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="178" spans="1:19" x14ac:dyDescent="0.6">
@@ -29132,7 +29140,7 @@
       </c>
       <c r="P178" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q178" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B178,Dangerous!$N:$N)</f>
@@ -29144,7 +29152,7 @@
       </c>
       <c r="S178" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="179" spans="1:19" x14ac:dyDescent="0.6">
@@ -29189,7 +29197,7 @@
       </c>
       <c r="P179" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q179" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B179,Dangerous!$N:$N)</f>
@@ -29201,7 +29209,7 @@
       </c>
       <c r="S179" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="180" spans="1:19" x14ac:dyDescent="0.6">
@@ -29246,7 +29254,7 @@
       </c>
       <c r="P180" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q180" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B180,Dangerous!$N:$N)</f>
@@ -29258,7 +29266,7 @@
       </c>
       <c r="S180" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="181" spans="1:19" x14ac:dyDescent="0.6">
@@ -29303,7 +29311,7 @@
       </c>
       <c r="P181" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q181" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B181,Dangerous!$N:$N)</f>
@@ -29315,7 +29323,7 @@
       </c>
       <c r="S181" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="182" spans="1:19" x14ac:dyDescent="0.6">
@@ -29360,7 +29368,7 @@
       </c>
       <c r="P182" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q182" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B182,Dangerous!$N:$N)</f>
@@ -29372,7 +29380,7 @@
       </c>
       <c r="S182" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="183" spans="1:19" x14ac:dyDescent="0.6">
@@ -29474,7 +29482,7 @@
       </c>
       <c r="P184" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q184" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B184,Dangerous!$N:$N)</f>
@@ -29486,7 +29494,7 @@
       </c>
       <c r="S184" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="185" spans="1:19" x14ac:dyDescent="0.6">
@@ -29531,7 +29539,7 @@
       </c>
       <c r="P185" s="30">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q185" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B185,Dangerous!$N:$N)</f>
@@ -29543,7 +29551,7 @@
       </c>
       <c r="S185" s="31">
         <f t="shared" si="5"/>
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:19" x14ac:dyDescent="0.6">
@@ -29588,7 +29596,7 @@
       </c>
       <c r="P186" s="30">
         <f t="shared" si="4"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q186" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B186,Dangerous!$N:$N)</f>
@@ -29600,7 +29608,7 @@
       </c>
       <c r="S186" s="31">
         <f t="shared" si="5"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="187" spans="1:19" x14ac:dyDescent="0.6">
@@ -29645,7 +29653,7 @@
       </c>
       <c r="P187" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q187" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B187,Dangerous!$N:$N)</f>
@@ -29657,7 +29665,7 @@
       </c>
       <c r="S187" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="188" spans="1:19" x14ac:dyDescent="0.6">
@@ -29702,7 +29710,7 @@
       </c>
       <c r="P188" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q188" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B188,Dangerous!$N:$N)</f>
@@ -29714,7 +29722,7 @@
       </c>
       <c r="S188" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="189" spans="1:19" x14ac:dyDescent="0.6">
@@ -29759,7 +29767,7 @@
       </c>
       <c r="P189" s="30">
         <f t="shared" si="4"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q189" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B189,Dangerous!$N:$N)</f>
@@ -29771,7 +29779,7 @@
       </c>
       <c r="S189" s="31">
         <f t="shared" si="5"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="190" spans="1:19" x14ac:dyDescent="0.6">
@@ -29816,7 +29824,7 @@
       </c>
       <c r="P190" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q190" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B190,Dangerous!$N:$N)</f>
@@ -29828,7 +29836,7 @@
       </c>
       <c r="S190" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="191" spans="1:19" x14ac:dyDescent="0.6">
@@ -29873,7 +29881,7 @@
       </c>
       <c r="P191" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q191" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B191,Dangerous!$N:$N)</f>
@@ -29885,7 +29893,7 @@
       </c>
       <c r="S191" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="192" spans="1:19" x14ac:dyDescent="0.6">
@@ -29930,7 +29938,7 @@
       </c>
       <c r="P192" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q192" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B192,Dangerous!$N:$N)</f>
@@ -29942,7 +29950,7 @@
       </c>
       <c r="S192" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="193" spans="1:19" x14ac:dyDescent="0.6">
@@ -29987,7 +29995,7 @@
       </c>
       <c r="P193" s="30">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q193" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B193,Dangerous!$N:$N)</f>
@@ -29999,7 +30007,7 @@
       </c>
       <c r="S193" s="31">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="194" spans="1:19" x14ac:dyDescent="0.6">
@@ -30044,7 +30052,7 @@
       </c>
       <c r="P194" s="30">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q194" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B194,Dangerous!$N:$N)</f>
@@ -30056,7 +30064,7 @@
       </c>
       <c r="S194" s="31">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="195" spans="1:19" x14ac:dyDescent="0.6">
@@ -30100,7 +30108,7 @@
         <v>0</v>
       </c>
       <c r="P195" s="30">
-        <f t="shared" ref="P195:P258" si="6">SUM(E195:O195)</f>
+        <f t="shared" ref="P195:P258" si="6">SUM(E195:N195)</f>
         <v>0</v>
       </c>
       <c r="Q195" s="29">
@@ -30158,7 +30166,7 @@
       </c>
       <c r="P196" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q196" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B196,Dangerous!$N:$N)</f>
@@ -30170,7 +30178,7 @@
       </c>
       <c r="S196" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="197" spans="1:19" x14ac:dyDescent="0.6">
@@ -30215,7 +30223,7 @@
       </c>
       <c r="P197" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q197" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B197,Dangerous!$N:$N)</f>
@@ -30227,7 +30235,7 @@
       </c>
       <c r="S197" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="198" spans="1:19" x14ac:dyDescent="0.6">
@@ -30272,7 +30280,7 @@
       </c>
       <c r="P198" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q198" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B198,Dangerous!$N:$N)</f>
@@ -30284,7 +30292,7 @@
       </c>
       <c r="S198" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="199" spans="1:19" x14ac:dyDescent="0.6">
@@ -30329,7 +30337,7 @@
       </c>
       <c r="P199" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q199" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B199,Dangerous!$N:$N)</f>
@@ -30341,7 +30349,7 @@
       </c>
       <c r="S199" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="200" spans="1:19" x14ac:dyDescent="0.6">
@@ -30386,7 +30394,7 @@
       </c>
       <c r="P200" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q200" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B200,Dangerous!$N:$N)</f>
@@ -30398,7 +30406,7 @@
       </c>
       <c r="S200" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="201" spans="1:19" x14ac:dyDescent="0.6">
@@ -30443,7 +30451,7 @@
       </c>
       <c r="P201" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q201" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B201,Dangerous!$N:$N)</f>
@@ -30455,7 +30463,7 @@
       </c>
       <c r="S201" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="202" spans="1:19" x14ac:dyDescent="0.6">
@@ -30500,7 +30508,7 @@
       </c>
       <c r="P202" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q202" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B202,Dangerous!$N:$N)</f>
@@ -30512,7 +30520,7 @@
       </c>
       <c r="S202" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="203" spans="1:19" x14ac:dyDescent="0.6">
@@ -30557,7 +30565,7 @@
       </c>
       <c r="P203" s="30">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q203" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B203,Dangerous!$N:$N)</f>
@@ -30569,7 +30577,7 @@
       </c>
       <c r="S203" s="31">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:19" x14ac:dyDescent="0.6">
@@ -30614,7 +30622,7 @@
       </c>
       <c r="P204" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q204" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B204,Dangerous!$N:$N)</f>
@@ -30626,7 +30634,7 @@
       </c>
       <c r="S204" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="205" spans="1:19" x14ac:dyDescent="0.6">
@@ -30671,7 +30679,7 @@
       </c>
       <c r="P205" s="30">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q205" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B205,Dangerous!$N:$N)</f>
@@ -30683,7 +30691,7 @@
       </c>
       <c r="S205" s="31">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="206" spans="1:19" x14ac:dyDescent="0.6">
@@ -30728,7 +30736,7 @@
       </c>
       <c r="P206" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q206" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B206,Dangerous!$N:$N)</f>
@@ -30740,7 +30748,7 @@
       </c>
       <c r="S206" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="207" spans="1:19" x14ac:dyDescent="0.6">
@@ -30785,7 +30793,7 @@
       </c>
       <c r="P207" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q207" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B207,Dangerous!$N:$N)</f>
@@ -30797,7 +30805,7 @@
       </c>
       <c r="S207" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="208" spans="1:19" x14ac:dyDescent="0.6">
@@ -30842,7 +30850,7 @@
       </c>
       <c r="P208" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q208" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B208,Dangerous!$N:$N)</f>
@@ -30854,7 +30862,7 @@
       </c>
       <c r="S208" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="209" spans="1:19" x14ac:dyDescent="0.6">
@@ -30899,7 +30907,7 @@
       </c>
       <c r="P209" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q209" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B209,Dangerous!$N:$N)</f>
@@ -30911,7 +30919,7 @@
       </c>
       <c r="S209" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="210" spans="1:19" x14ac:dyDescent="0.6">
@@ -30956,7 +30964,7 @@
       </c>
       <c r="P210" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q210" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B210,Dangerous!$N:$N)</f>
@@ -30968,7 +30976,7 @@
       </c>
       <c r="S210" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="211" spans="1:19" x14ac:dyDescent="0.6">
@@ -31013,7 +31021,7 @@
       </c>
       <c r="P211" s="30">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q211" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B211,Dangerous!$N:$N)</f>
@@ -31025,7 +31033,7 @@
       </c>
       <c r="S211" s="31">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:19" x14ac:dyDescent="0.6">
@@ -31070,7 +31078,7 @@
       </c>
       <c r="P212" s="30">
         <f t="shared" si="6"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q212" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B212,Dangerous!$N:$N)</f>
@@ -31082,7 +31090,7 @@
       </c>
       <c r="S212" s="31">
         <f t="shared" si="7"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="213" spans="1:19" x14ac:dyDescent="0.6">
@@ -31127,7 +31135,7 @@
       </c>
       <c r="P213" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q213" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B213,Dangerous!$N:$N)</f>
@@ -31139,7 +31147,7 @@
       </c>
       <c r="S213" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="214" spans="1:19" x14ac:dyDescent="0.6">
@@ -31184,7 +31192,7 @@
       </c>
       <c r="P214" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q214" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B214,Dangerous!$N:$N)</f>
@@ -31196,7 +31204,7 @@
       </c>
       <c r="S214" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="215" spans="1:19" x14ac:dyDescent="0.6">
@@ -31241,7 +31249,7 @@
       </c>
       <c r="P215" s="30">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q215" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B215,Dangerous!$N:$N)</f>
@@ -31253,7 +31261,7 @@
       </c>
       <c r="S215" s="31">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:19" x14ac:dyDescent="0.6">
@@ -31298,7 +31306,7 @@
       </c>
       <c r="P216" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q216" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B216,Dangerous!$N:$N)</f>
@@ -31310,7 +31318,7 @@
       </c>
       <c r="S216" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="217" spans="1:19" x14ac:dyDescent="0.6">
@@ -31355,7 +31363,7 @@
       </c>
       <c r="P217" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q217" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B217,Dangerous!$N:$N)</f>
@@ -31367,7 +31375,7 @@
       </c>
       <c r="S217" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="218" spans="1:19" x14ac:dyDescent="0.6">
@@ -31412,7 +31420,7 @@
       </c>
       <c r="P218" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q218" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B218,Dangerous!$N:$N)</f>
@@ -31424,7 +31432,7 @@
       </c>
       <c r="S218" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="219" spans="1:19" x14ac:dyDescent="0.6">
@@ -31469,7 +31477,7 @@
       </c>
       <c r="P219" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q219" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B219,Dangerous!$N:$N)</f>
@@ -31481,7 +31489,7 @@
       </c>
       <c r="S219" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="220" spans="1:19" x14ac:dyDescent="0.6">
@@ -31526,7 +31534,7 @@
       </c>
       <c r="P220" s="30">
         <f t="shared" si="6"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q220" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B220,Dangerous!$N:$N)</f>
@@ -31538,7 +31546,7 @@
       </c>
       <c r="S220" s="31">
         <f t="shared" si="7"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="221" spans="1:19" x14ac:dyDescent="0.6">
@@ -31583,7 +31591,7 @@
       </c>
       <c r="P221" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q221" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B221,Dangerous!$N:$N)</f>
@@ -31595,7 +31603,7 @@
       </c>
       <c r="S221" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="222" spans="1:19" x14ac:dyDescent="0.6">
@@ -31640,7 +31648,7 @@
       </c>
       <c r="P222" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q222" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B222,Dangerous!$N:$N)</f>
@@ -31652,7 +31660,7 @@
       </c>
       <c r="S222" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="223" spans="1:19" x14ac:dyDescent="0.6">
@@ -31697,7 +31705,7 @@
       </c>
       <c r="P223" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q223" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B223,Dangerous!$N:$N)</f>
@@ -31709,7 +31717,7 @@
       </c>
       <c r="S223" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="224" spans="1:19" x14ac:dyDescent="0.6">
@@ -31754,7 +31762,7 @@
       </c>
       <c r="P224" s="30">
         <f t="shared" si="6"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q224" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B224,Dangerous!$N:$N)</f>
@@ -31766,7 +31774,7 @@
       </c>
       <c r="S224" s="31">
         <f t="shared" si="7"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="225" spans="1:19" x14ac:dyDescent="0.6">
@@ -31811,7 +31819,7 @@
       </c>
       <c r="P225" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q225" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B225,Dangerous!$N:$N)</f>
@@ -31823,7 +31831,7 @@
       </c>
       <c r="S225" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="226" spans="1:19" x14ac:dyDescent="0.6">
@@ -31868,7 +31876,7 @@
       </c>
       <c r="P226" s="30">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q226" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B226,Dangerous!$N:$N)</f>
@@ -31880,7 +31888,7 @@
       </c>
       <c r="S226" s="31">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:19" x14ac:dyDescent="0.6">
@@ -31925,7 +31933,7 @@
       </c>
       <c r="P227" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q227" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B227,Dangerous!$N:$N)</f>
@@ -31937,7 +31945,7 @@
       </c>
       <c r="S227" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="228" spans="1:19" x14ac:dyDescent="0.6">
@@ -31982,7 +31990,7 @@
       </c>
       <c r="P228" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q228" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B228,Dangerous!$N:$N)</f>
@@ -31994,7 +32002,7 @@
       </c>
       <c r="S228" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="229" spans="1:19" x14ac:dyDescent="0.6">
@@ -32039,7 +32047,7 @@
       </c>
       <c r="P229" s="30">
         <f t="shared" si="6"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q229" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B229,Dangerous!$N:$N)</f>
@@ -32051,7 +32059,7 @@
       </c>
       <c r="S229" s="31">
         <f t="shared" si="7"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="230" spans="1:19" x14ac:dyDescent="0.6">
@@ -32153,7 +32161,7 @@
       </c>
       <c r="P231" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q231" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B231,Dangerous!$N:$N)</f>
@@ -32165,7 +32173,7 @@
       </c>
       <c r="S231" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="232" spans="1:19" x14ac:dyDescent="0.6">
@@ -32210,7 +32218,7 @@
       </c>
       <c r="P232" s="30">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q232" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B232,Dangerous!$N:$N)</f>
@@ -32222,7 +32230,7 @@
       </c>
       <c r="S232" s="31">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:19" x14ac:dyDescent="0.6">
@@ -32324,7 +32332,7 @@
       </c>
       <c r="P234" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q234" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B234,Dangerous!$N:$N)</f>
@@ -32336,7 +32344,7 @@
       </c>
       <c r="S234" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="235" spans="1:19" x14ac:dyDescent="0.6">
@@ -32381,7 +32389,7 @@
       </c>
       <c r="P235" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q235" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B235,Dangerous!$N:$N)</f>
@@ -32393,7 +32401,7 @@
       </c>
       <c r="S235" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="236" spans="1:19" x14ac:dyDescent="0.6">
@@ -32438,7 +32446,7 @@
       </c>
       <c r="P236" s="30">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q236" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B236,Dangerous!$N:$N)</f>
@@ -32450,7 +32458,7 @@
       </c>
       <c r="S236" s="31">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:19" x14ac:dyDescent="0.6">
@@ -32495,7 +32503,7 @@
       </c>
       <c r="P237" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q237" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B237,Dangerous!$N:$N)</f>
@@ -32507,7 +32515,7 @@
       </c>
       <c r="S237" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="238" spans="1:19" x14ac:dyDescent="0.6">
@@ -32552,7 +32560,7 @@
       </c>
       <c r="P238" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q238" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B238,Dangerous!$N:$N)</f>
@@ -32564,7 +32572,7 @@
       </c>
       <c r="S238" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="239" spans="1:19" x14ac:dyDescent="0.6">
@@ -32609,7 +32617,7 @@
       </c>
       <c r="P239" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q239" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B239,Dangerous!$N:$N)</f>
@@ -32621,7 +32629,7 @@
       </c>
       <c r="S239" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="240" spans="1:19" x14ac:dyDescent="0.6">
@@ -32666,7 +32674,7 @@
       </c>
       <c r="P240" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q240" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B240,Dangerous!$N:$N)</f>
@@ -32678,7 +32686,7 @@
       </c>
       <c r="S240" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="241" spans="1:19" x14ac:dyDescent="0.6">
@@ -32723,7 +32731,7 @@
       </c>
       <c r="P241" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q241" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B241,Dangerous!$N:$N)</f>
@@ -32735,7 +32743,7 @@
       </c>
       <c r="S241" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="242" spans="1:19" x14ac:dyDescent="0.6">
@@ -32780,7 +32788,7 @@
       </c>
       <c r="P242" s="30">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q242" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B242,Dangerous!$N:$N)</f>
@@ -32792,7 +32800,7 @@
       </c>
       <c r="S242" s="31">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:19" x14ac:dyDescent="0.6">
@@ -32837,7 +32845,7 @@
       </c>
       <c r="P243" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q243" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B243,Dangerous!$N:$N)</f>
@@ -32849,7 +32857,7 @@
       </c>
       <c r="S243" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="244" spans="1:19" x14ac:dyDescent="0.6">
@@ -32894,7 +32902,7 @@
       </c>
       <c r="P244" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q244" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B244,Dangerous!$N:$N)</f>
@@ -32906,7 +32914,7 @@
       </c>
       <c r="S244" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="245" spans="1:19" x14ac:dyDescent="0.6">
@@ -32951,7 +32959,7 @@
       </c>
       <c r="P245" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q245" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B245,Dangerous!$N:$N)</f>
@@ -32963,7 +32971,7 @@
       </c>
       <c r="S245" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="246" spans="1:19" x14ac:dyDescent="0.6">
@@ -33008,7 +33016,7 @@
       </c>
       <c r="P246" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q246" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B246,Dangerous!$N:$N)</f>
@@ -33020,7 +33028,7 @@
       </c>
       <c r="S246" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="247" spans="1:19" x14ac:dyDescent="0.6">
@@ -33065,7 +33073,7 @@
       </c>
       <c r="P247" s="30">
         <f t="shared" si="6"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q247" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B247,Dangerous!$N:$N)</f>
@@ -33077,7 +33085,7 @@
       </c>
       <c r="S247" s="31">
         <f t="shared" si="7"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="248" spans="1:19" x14ac:dyDescent="0.6">
@@ -33122,7 +33130,7 @@
       </c>
       <c r="P248" s="30">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q248" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B248,Dangerous!$N:$N)</f>
@@ -33134,7 +33142,7 @@
       </c>
       <c r="S248" s="31">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:19" x14ac:dyDescent="0.6">
@@ -33179,7 +33187,7 @@
       </c>
       <c r="P249" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q249" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B249,Dangerous!$N:$N)</f>
@@ -33191,7 +33199,7 @@
       </c>
       <c r="S249" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="250" spans="1:19" x14ac:dyDescent="0.6">
@@ -33236,7 +33244,7 @@
       </c>
       <c r="P250" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q250" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B250,Dangerous!$N:$N)</f>
@@ -33248,7 +33256,7 @@
       </c>
       <c r="S250" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="251" spans="1:19" x14ac:dyDescent="0.6">
@@ -33293,7 +33301,7 @@
       </c>
       <c r="P251" s="30">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q251" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B251,Dangerous!$N:$N)</f>
@@ -33305,7 +33313,7 @@
       </c>
       <c r="S251" s="31">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:19" x14ac:dyDescent="0.6">
@@ -33350,7 +33358,7 @@
       </c>
       <c r="P252" s="30">
         <f t="shared" si="6"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q252" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B252,Dangerous!$N:$N)</f>
@@ -33362,7 +33370,7 @@
       </c>
       <c r="S252" s="31">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="253" spans="1:19" x14ac:dyDescent="0.6">
@@ -33407,7 +33415,7 @@
       </c>
       <c r="P253" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q253" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B253,Dangerous!$N:$N)</f>
@@ -33419,7 +33427,7 @@
       </c>
       <c r="S253" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="254" spans="1:19" x14ac:dyDescent="0.6">
@@ -33464,7 +33472,7 @@
       </c>
       <c r="P254" s="30">
         <f t="shared" si="6"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q254" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B254,Dangerous!$N:$N)</f>
@@ -33476,7 +33484,7 @@
       </c>
       <c r="S254" s="31">
         <f t="shared" si="7"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="255" spans="1:19" x14ac:dyDescent="0.6">
@@ -33521,7 +33529,7 @@
       </c>
       <c r="P255" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q255" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B255,Dangerous!$N:$N)</f>
@@ -33533,7 +33541,7 @@
       </c>
       <c r="S255" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="256" spans="1:19" x14ac:dyDescent="0.6">
@@ -33578,7 +33586,7 @@
       </c>
       <c r="P256" s="30">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q256" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B256,Dangerous!$N:$N)</f>
@@ -33590,7 +33598,7 @@
       </c>
       <c r="S256" s="31">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:19" x14ac:dyDescent="0.6">
@@ -33635,7 +33643,7 @@
       </c>
       <c r="P257" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q257" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B257,Dangerous!$N:$N)</f>
@@ -33647,7 +33655,7 @@
       </c>
       <c r="S257" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="258" spans="1:19" x14ac:dyDescent="0.6">
@@ -33692,7 +33700,7 @@
       </c>
       <c r="P258" s="30">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q258" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B258,Dangerous!$N:$N)</f>
@@ -33704,7 +33712,7 @@
       </c>
       <c r="S258" s="31">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="259" spans="1:19" x14ac:dyDescent="0.6">
@@ -33748,7 +33756,7 @@
         <v>0</v>
       </c>
       <c r="P259" s="30">
-        <f t="shared" ref="P259:P286" si="8">SUM(E259:O259)</f>
+        <f t="shared" ref="P259:P292" si="8">SUM(E259:N259)</f>
         <v>0</v>
       </c>
       <c r="Q259" s="29">
@@ -33806,7 +33814,7 @@
       </c>
       <c r="P260" s="30">
         <f t="shared" si="8"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q260" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B260,Dangerous!$N:$N)</f>
@@ -33818,7 +33826,7 @@
       </c>
       <c r="S260" s="31">
         <f t="shared" si="9"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="261" spans="1:19" x14ac:dyDescent="0.6">
@@ -33863,7 +33871,7 @@
       </c>
       <c r="P261" s="30">
         <f t="shared" si="8"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q261" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B261,Dangerous!$N:$N)</f>
@@ -33875,7 +33883,7 @@
       </c>
       <c r="S261" s="31">
         <f t="shared" si="9"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="262" spans="1:19" x14ac:dyDescent="0.6">
@@ -33920,7 +33928,7 @@
       </c>
       <c r="P262" s="30">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q262" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B262,Dangerous!$N:$N)</f>
@@ -33932,7 +33940,7 @@
       </c>
       <c r="S262" s="31">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:19" x14ac:dyDescent="0.6">
@@ -33977,7 +33985,7 @@
       </c>
       <c r="P263" s="30">
         <f t="shared" si="8"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q263" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B263,Dangerous!$N:$N)</f>
@@ -33989,7 +33997,7 @@
       </c>
       <c r="S263" s="31">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="264" spans="1:19" x14ac:dyDescent="0.6">
@@ -34034,7 +34042,7 @@
       </c>
       <c r="P264" s="30">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q264" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B264,Dangerous!$N:$N)</f>
@@ -34046,7 +34054,7 @@
       </c>
       <c r="S264" s="31">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="265" spans="1:19" x14ac:dyDescent="0.6">
@@ -34148,7 +34156,7 @@
       </c>
       <c r="P266" s="30">
         <f t="shared" si="8"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q266" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B266,Dangerous!$N:$N)</f>
@@ -34160,7 +34168,7 @@
       </c>
       <c r="S266" s="31">
         <f t="shared" si="9"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="267" spans="1:19" x14ac:dyDescent="0.6">
@@ -34205,7 +34213,7 @@
       </c>
       <c r="P267" s="30">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q267" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B267,Dangerous!$N:$N)</f>
@@ -34217,7 +34225,7 @@
       </c>
       <c r="S267" s="31">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:19" x14ac:dyDescent="0.6">
@@ -34319,7 +34327,7 @@
       </c>
       <c r="P269" s="30">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q269" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B269,Dangerous!$N:$N)</f>
@@ -34331,7 +34339,7 @@
       </c>
       <c r="S269" s="31">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="270" spans="1:19" x14ac:dyDescent="0.6">
@@ -34433,7 +34441,7 @@
       </c>
       <c r="P271" s="30">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q271" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B271,Dangerous!$N:$N)</f>
@@ -34445,7 +34453,7 @@
       </c>
       <c r="S271" s="31">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:19" x14ac:dyDescent="0.6">
@@ -34547,7 +34555,7 @@
       </c>
       <c r="P273" s="30">
         <f t="shared" si="8"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q273" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B273,Dangerous!$N:$N)</f>
@@ -34559,7 +34567,7 @@
       </c>
       <c r="S273" s="31">
         <f t="shared" si="9"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="274" spans="1:19" x14ac:dyDescent="0.6">
@@ -34604,7 +34612,7 @@
       </c>
       <c r="P274" s="30">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q274" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B274,Dangerous!$N:$N)</f>
@@ -34616,7 +34624,7 @@
       </c>
       <c r="S274" s="31">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="275" spans="1:19" x14ac:dyDescent="0.6">
@@ -34718,7 +34726,7 @@
       </c>
       <c r="P276" s="30">
         <f t="shared" si="8"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q276" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B276,Dangerous!$N:$N)</f>
@@ -34730,7 +34738,7 @@
       </c>
       <c r="S276" s="31">
         <f t="shared" si="9"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="277" spans="1:19" x14ac:dyDescent="0.6">
@@ -34775,7 +34783,7 @@
       </c>
       <c r="P277" s="30">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q277" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B277,Dangerous!$N:$N)</f>
@@ -34787,7 +34795,7 @@
       </c>
       <c r="S277" s="31">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="278" spans="1:19" x14ac:dyDescent="0.6">
@@ -34889,7 +34897,7 @@
       </c>
       <c r="P279" s="30">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q279" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B279,Dangerous!$N:$N)</f>
@@ -34901,7 +34909,7 @@
       </c>
       <c r="S279" s="31">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="280" spans="1:19" x14ac:dyDescent="0.6">
@@ -34946,7 +34954,7 @@
       </c>
       <c r="P280" s="30">
         <f t="shared" si="8"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q280" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B280,Dangerous!$N:$N)</f>
@@ -34958,7 +34966,7 @@
       </c>
       <c r="S280" s="31">
         <f t="shared" si="9"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="281" spans="1:19" x14ac:dyDescent="0.6">
@@ -35003,7 +35011,7 @@
       </c>
       <c r="P281" s="30">
         <f t="shared" si="8"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q281" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B281,Dangerous!$N:$N)</f>
@@ -35015,7 +35023,7 @@
       </c>
       <c r="S281" s="31">
         <f t="shared" si="9"/>
-        <v>17.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="282" spans="1:19" x14ac:dyDescent="0.6">
@@ -35060,7 +35068,7 @@
       </c>
       <c r="P282" s="30">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q282" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B282,Dangerous!$N:$N)</f>
@@ -35072,7 +35080,7 @@
       </c>
       <c r="S282" s="31">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="283" spans="1:19" x14ac:dyDescent="0.6">
@@ -35117,7 +35125,7 @@
       </c>
       <c r="P283" s="30">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="Q283" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B283,Dangerous!$N:$N)</f>
@@ -35129,7 +35137,7 @@
       </c>
       <c r="S283" s="31">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="284" spans="1:19" x14ac:dyDescent="0.6">
@@ -35174,7 +35182,7 @@
       </c>
       <c r="P284" s="30">
         <f t="shared" si="8"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q284" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B284,Dangerous!$N:$N)</f>
@@ -35186,7 +35194,7 @@
       </c>
       <c r="S284" s="31">
         <f t="shared" si="9"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="285" spans="1:19" x14ac:dyDescent="0.6">
@@ -35231,7 +35239,7 @@
       </c>
       <c r="P285" s="30">
         <f t="shared" si="8"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q285" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B285,Dangerous!$N:$N)</f>
@@ -35243,7 +35251,7 @@
       </c>
       <c r="S285" s="31">
         <f t="shared" si="9"/>
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="286" spans="1:19" x14ac:dyDescent="0.6">
@@ -35288,7 +35296,7 @@
       </c>
       <c r="P286" s="30">
         <f t="shared" si="8"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q286" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B286,Dangerous!$N:$N)</f>
@@ -35300,7 +35308,7 @@
       </c>
       <c r="S286" s="31">
         <f t="shared" si="9"/>
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="287" spans="1:19" x14ac:dyDescent="0.6">
@@ -35344,8 +35352,8 @@
         <v>6.25</v>
       </c>
       <c r="P287" s="30">
-        <f t="shared" ref="P287" si="10">SUM(E287:O287)</f>
-        <v>12.5</v>
+        <f t="shared" si="8"/>
+        <v>6.25</v>
       </c>
       <c r="Q287" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B287,Dangerous!$N:$N)</f>
@@ -35356,8 +35364,8 @@
         <v>0</v>
       </c>
       <c r="S287" s="31">
-        <f t="shared" ref="S287" si="11">SUM(P287:R287)</f>
-        <v>12.5</v>
+        <f t="shared" ref="S287" si="10">SUM(P287:R287)</f>
+        <v>6.25</v>
       </c>
     </row>
     <row r="288" spans="1:19" x14ac:dyDescent="0.6">
@@ -35401,8 +35409,8 @@
         <v>5</v>
       </c>
       <c r="P288" s="29">
-        <f t="shared" ref="P288:P292" si="12">SUM(E288:O288)</f>
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="Q288" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B288,Dangerous!$N:$N)</f>
@@ -35413,8 +35421,8 @@
         <v>0</v>
       </c>
       <c r="S288" s="31">
-        <f t="shared" ref="S288:S292" si="13">SUM(P288:R288)</f>
-        <v>10</v>
+        <f t="shared" ref="S288:S292" si="11">SUM(P288:R288)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:19" x14ac:dyDescent="0.6">
@@ -35458,8 +35466,8 @@
         <v>1.25</v>
       </c>
       <c r="P289" s="29">
-        <f t="shared" si="12"/>
-        <v>2.5</v>
+        <f t="shared" si="8"/>
+        <v>1.25</v>
       </c>
       <c r="Q289" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B289,Dangerous!$N:$N)</f>
@@ -35470,8 +35478,8 @@
         <v>0</v>
       </c>
       <c r="S289" s="31">
-        <f t="shared" si="13"/>
-        <v>2.5</v>
+        <f t="shared" si="11"/>
+        <v>1.25</v>
       </c>
     </row>
     <row r="290" spans="1:19" x14ac:dyDescent="0.6">
@@ -35515,8 +35523,8 @@
         <v>6.25</v>
       </c>
       <c r="P290" s="29">
-        <f t="shared" si="12"/>
-        <v>12.5</v>
+        <f t="shared" si="8"/>
+        <v>6.25</v>
       </c>
       <c r="Q290" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B290,Dangerous!$N:$N)</f>
@@ -35527,8 +35535,8 @@
         <v>0</v>
       </c>
       <c r="S290" s="31">
-        <f t="shared" si="13"/>
-        <v>12.5</v>
+        <f t="shared" si="11"/>
+        <v>6.25</v>
       </c>
     </row>
     <row r="291" spans="1:19" x14ac:dyDescent="0.6">
@@ -35572,8 +35580,8 @@
         <v>5</v>
       </c>
       <c r="P291" s="29">
-        <f t="shared" si="12"/>
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="Q291" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B291,Dangerous!$N:$N)</f>
@@ -35584,8 +35592,8 @@
         <v>0</v>
       </c>
       <c r="S291" s="31">
-        <f t="shared" si="13"/>
-        <v>10</v>
+        <f t="shared" si="11"/>
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:19" x14ac:dyDescent="0.6">
@@ -35629,7 +35637,7 @@
         <v>0</v>
       </c>
       <c r="P292" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q292" s="29">
@@ -35641,11 +35649,12 @@
         <v>0</v>
       </c>
       <c r="S292" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:S292" xr:uid="{F842C06B-732A-4C8F-AF4C-77852CE1F2C1}"/>
   <conditionalFormatting sqref="E2:O217 E219:O287">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>0.55</formula>

--- a/source-excel/CPK.xlsx
+++ b/source-excel/CPK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\newstarrating\source-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F289D415-64EF-4F85-9295-939C9E20A337}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64EC813E-3A5F-4415-A21F-3C65CC1E7C3E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" activeTab="1" xr2:uid="{A8A91EEF-99CC-4EB3-BE03-3D899D5B1C9B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" activeTab="2" xr2:uid="{A8A91EEF-99CC-4EB3-BE03-3D899D5B1C9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Q" sheetId="3" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Manual" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Dangerous!$A$1:$N$287</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Q!$A$1:$Q$291</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Q-Score'!$A$1:$S$292</definedName>
   </definedNames>
@@ -22361,7 +22362,7 @@
       </c>
       <c r="Q59" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B59,Dangerous!$N:$N)</f>
-        <v>-2.5</v>
+        <v>-5</v>
       </c>
       <c r="R59" s="29">
         <f>SUMIF(Manual!$A:$A,'Q-Score'!$B59,Manual!$N:$N)</f>
@@ -22369,7 +22370,7 @@
       </c>
       <c r="S59" s="31">
         <f t="shared" si="1"/>
-        <v>-2.5</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.6">
@@ -22703,7 +22704,7 @@
       </c>
       <c r="Q65" s="29">
         <f>SUMIF(Dangerous!$A:$A,'Q-Score'!$B65,Dangerous!$N:$N)</f>
-        <v>-2.5</v>
+        <v>-5</v>
       </c>
       <c r="R65" s="29">
         <f>SUMIF(Manual!$A:$A,'Q-Score'!$B65,Manual!$N:$N)</f>
@@ -22711,7 +22712,7 @@
       </c>
       <c r="S65" s="31">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.6">
@@ -35743,6 +35744,7 @@
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="23">
+        <f>SUM(C2:M2)</f>
         <v>0</v>
       </c>
     </row>
@@ -35765,6 +35767,7 @@
       <c r="L3" s="22"/>
       <c r="M3" s="22"/>
       <c r="N3" s="23">
+        <f t="shared" ref="N3:N66" si="0">SUM(C3:M3)</f>
         <v>0</v>
       </c>
     </row>
@@ -35787,6 +35790,7 @@
       <c r="L4" s="22"/>
       <c r="M4" s="22"/>
       <c r="N4" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -35809,6 +35813,7 @@
       <c r="L5" s="22"/>
       <c r="M5" s="22"/>
       <c r="N5" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -35831,6 +35836,7 @@
       <c r="L6" s="22"/>
       <c r="M6" s="22"/>
       <c r="N6" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -35853,6 +35859,7 @@
       <c r="L7" s="22"/>
       <c r="M7" s="22"/>
       <c r="N7" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -35875,6 +35882,7 @@
       <c r="L8" s="22"/>
       <c r="M8" s="22"/>
       <c r="N8" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -35897,6 +35905,7 @@
       <c r="L9" s="22"/>
       <c r="M9" s="22"/>
       <c r="N9" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -35919,6 +35928,7 @@
       <c r="L10" s="22"/>
       <c r="M10" s="22"/>
       <c r="N10" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -35941,6 +35951,7 @@
       <c r="L11" s="22"/>
       <c r="M11" s="22"/>
       <c r="N11" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -35963,6 +35974,7 @@
       <c r="L12" s="22"/>
       <c r="M12" s="22"/>
       <c r="N12" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -35985,6 +35997,7 @@
       <c r="L13" s="22"/>
       <c r="M13" s="22"/>
       <c r="N13" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36007,6 +36020,7 @@
       <c r="L14" s="22"/>
       <c r="M14" s="22"/>
       <c r="N14" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36029,6 +36043,7 @@
       <c r="L15" s="22"/>
       <c r="M15" s="22"/>
       <c r="N15" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36051,6 +36066,7 @@
       <c r="L16" s="22"/>
       <c r="M16" s="22"/>
       <c r="N16" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36073,6 +36089,7 @@
       <c r="L17" s="22"/>
       <c r="M17" s="22"/>
       <c r="N17" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36095,6 +36112,7 @@
       <c r="L18" s="22"/>
       <c r="M18" s="22"/>
       <c r="N18" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36117,6 +36135,7 @@
       <c r="L19" s="22"/>
       <c r="M19" s="22"/>
       <c r="N19" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36139,6 +36158,7 @@
       <c r="L20" s="22"/>
       <c r="M20" s="22"/>
       <c r="N20" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36161,6 +36181,7 @@
       <c r="L21" s="22"/>
       <c r="M21" s="22"/>
       <c r="N21" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36183,6 +36204,7 @@
       <c r="L22" s="22"/>
       <c r="M22" s="22"/>
       <c r="N22" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36205,6 +36227,7 @@
       <c r="L23" s="22"/>
       <c r="M23" s="22"/>
       <c r="N23" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36227,6 +36250,7 @@
       <c r="L24" s="22"/>
       <c r="M24" s="22"/>
       <c r="N24" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36249,6 +36273,7 @@
       <c r="L25" s="22"/>
       <c r="M25" s="22"/>
       <c r="N25" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36271,6 +36296,7 @@
       <c r="L26" s="22"/>
       <c r="M26" s="22"/>
       <c r="N26" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36293,6 +36319,7 @@
       <c r="L27" s="22"/>
       <c r="M27" s="22"/>
       <c r="N27" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36315,6 +36342,7 @@
       <c r="L28" s="22"/>
       <c r="M28" s="22"/>
       <c r="N28" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36337,6 +36365,7 @@
       <c r="L29" s="22"/>
       <c r="M29" s="22"/>
       <c r="N29" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36359,6 +36388,7 @@
       <c r="L30" s="22"/>
       <c r="M30" s="22"/>
       <c r="N30" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36381,6 +36411,7 @@
       <c r="L31" s="22"/>
       <c r="M31" s="22"/>
       <c r="N31" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36403,6 +36434,7 @@
       <c r="L32" s="22"/>
       <c r="M32" s="22"/>
       <c r="N32" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36425,6 +36457,7 @@
       <c r="L33" s="22"/>
       <c r="M33" s="22"/>
       <c r="N33" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36447,6 +36480,7 @@
       <c r="L34" s="22"/>
       <c r="M34" s="22"/>
       <c r="N34" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36469,6 +36503,7 @@
       <c r="L35" s="22"/>
       <c r="M35" s="22"/>
       <c r="N35" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36491,6 +36526,7 @@
       <c r="L36" s="22"/>
       <c r="M36" s="22"/>
       <c r="N36" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36513,6 +36549,7 @@
       <c r="L37" s="22"/>
       <c r="M37" s="22"/>
       <c r="N37" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36535,6 +36572,7 @@
       <c r="L38" s="22"/>
       <c r="M38" s="22"/>
       <c r="N38" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36557,6 +36595,7 @@
       <c r="L39" s="22"/>
       <c r="M39" s="22"/>
       <c r="N39" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36579,6 +36618,7 @@
       <c r="L40" s="22"/>
       <c r="M40" s="22"/>
       <c r="N40" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36601,6 +36641,7 @@
       <c r="L41" s="22"/>
       <c r="M41" s="22"/>
       <c r="N41" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36623,6 +36664,7 @@
       <c r="L42" s="22"/>
       <c r="M42" s="22"/>
       <c r="N42" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36645,6 +36687,7 @@
       <c r="L43" s="22"/>
       <c r="M43" s="22"/>
       <c r="N43" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36667,6 +36710,7 @@
       <c r="L44" s="22"/>
       <c r="M44" s="22"/>
       <c r="N44" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36689,6 +36733,7 @@
       <c r="L45" s="22"/>
       <c r="M45" s="22"/>
       <c r="N45" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36713,6 +36758,7 @@
       <c r="L46" s="22"/>
       <c r="M46" s="22"/>
       <c r="N46" s="23">
+        <f t="shared" si="0"/>
         <v>-2.5</v>
       </c>
     </row>
@@ -36732,12 +36778,15 @@
       <c r="I47" s="22">
         <v>-2.5</v>
       </c>
-      <c r="J47" s="22"/>
+      <c r="J47" s="22">
+        <v>-2.5</v>
+      </c>
       <c r="K47" s="22"/>
       <c r="L47" s="22"/>
       <c r="M47" s="22"/>
       <c r="N47" s="23">
-        <v>-2.5</v>
+        <f t="shared" si="0"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.6">
@@ -36759,6 +36808,7 @@
       <c r="L48" s="22"/>
       <c r="M48" s="22"/>
       <c r="N48" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36781,6 +36831,7 @@
       <c r="L49" s="22"/>
       <c r="M49" s="22"/>
       <c r="N49" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36803,6 +36854,7 @@
       <c r="L50" s="22"/>
       <c r="M50" s="22"/>
       <c r="N50" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36825,6 +36877,7 @@
       <c r="L51" s="22"/>
       <c r="M51" s="22"/>
       <c r="N51" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36844,12 +36897,15 @@
         <v>-2.5</v>
       </c>
       <c r="I52" s="22"/>
-      <c r="J52" s="22"/>
+      <c r="J52" s="22">
+        <v>-2.5</v>
+      </c>
       <c r="K52" s="22"/>
       <c r="L52" s="22"/>
       <c r="M52" s="22"/>
       <c r="N52" s="23">
-        <v>-2.5</v>
+        <f t="shared" si="0"/>
+        <v>-5</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.6">
@@ -36871,6 +36927,7 @@
       <c r="L53" s="22"/>
       <c r="M53" s="22"/>
       <c r="N53" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36893,6 +36950,7 @@
       <c r="L54" s="22"/>
       <c r="M54" s="22"/>
       <c r="N54" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36915,6 +36973,7 @@
       <c r="L55" s="22"/>
       <c r="M55" s="22"/>
       <c r="N55" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36937,6 +36996,7 @@
       <c r="L56" s="22"/>
       <c r="M56" s="22"/>
       <c r="N56" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36959,6 +37019,7 @@
       <c r="L57" s="22"/>
       <c r="M57" s="22"/>
       <c r="N57" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -36981,6 +37042,7 @@
       <c r="L58" s="22"/>
       <c r="M58" s="22"/>
       <c r="N58" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -37003,6 +37065,7 @@
       <c r="L59" s="22"/>
       <c r="M59" s="22"/>
       <c r="N59" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -37025,6 +37088,7 @@
       <c r="L60" s="22"/>
       <c r="M60" s="22"/>
       <c r="N60" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -37047,6 +37111,7 @@
       <c r="L61" s="22"/>
       <c r="M61" s="22"/>
       <c r="N61" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -37069,6 +37134,7 @@
       <c r="L62" s="22"/>
       <c r="M62" s="22"/>
       <c r="N62" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -37093,6 +37159,7 @@
       <c r="L63" s="22"/>
       <c r="M63" s="22"/>
       <c r="N63" s="23">
+        <f t="shared" si="0"/>
         <v>-2.5</v>
       </c>
     </row>
@@ -37115,6 +37182,7 @@
       <c r="L64" s="22"/>
       <c r="M64" s="22"/>
       <c r="N64" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -37137,6 +37205,7 @@
       <c r="L65" s="22"/>
       <c r="M65" s="22"/>
       <c r="N65" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -37159,6 +37228,7 @@
       <c r="L66" s="22"/>
       <c r="M66" s="22"/>
       <c r="N66" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -37181,6 +37251,7 @@
       <c r="L67" s="22"/>
       <c r="M67" s="22"/>
       <c r="N67" s="23">
+        <f t="shared" ref="N67:N130" si="1">SUM(C67:M67)</f>
         <v>0</v>
       </c>
     </row>
@@ -37203,6 +37274,7 @@
       <c r="L68" s="22"/>
       <c r="M68" s="22"/>
       <c r="N68" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37225,6 +37297,7 @@
       <c r="L69" s="22"/>
       <c r="M69" s="22"/>
       <c r="N69" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37247,6 +37320,7 @@
       <c r="L70" s="22"/>
       <c r="M70" s="22"/>
       <c r="N70" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37269,6 +37343,7 @@
       <c r="L71" s="22"/>
       <c r="M71" s="22"/>
       <c r="N71" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37291,6 +37366,7 @@
       <c r="L72" s="22"/>
       <c r="M72" s="22"/>
       <c r="N72" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37313,6 +37389,7 @@
       <c r="L73" s="22"/>
       <c r="M73" s="22"/>
       <c r="N73" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37335,6 +37412,7 @@
       <c r="L74" s="22"/>
       <c r="M74" s="22"/>
       <c r="N74" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37357,6 +37435,7 @@
       <c r="L75" s="22"/>
       <c r="M75" s="22"/>
       <c r="N75" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37379,6 +37458,7 @@
       <c r="L76" s="22"/>
       <c r="M76" s="22"/>
       <c r="N76" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37401,6 +37481,7 @@
       <c r="L77" s="22"/>
       <c r="M77" s="22"/>
       <c r="N77" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37423,6 +37504,7 @@
       <c r="L78" s="22"/>
       <c r="M78" s="22"/>
       <c r="N78" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37445,6 +37527,7 @@
       <c r="L79" s="22"/>
       <c r="M79" s="22"/>
       <c r="N79" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37467,6 +37550,7 @@
       <c r="L80" s="22"/>
       <c r="M80" s="22"/>
       <c r="N80" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37489,6 +37573,7 @@
       <c r="L81" s="22"/>
       <c r="M81" s="22"/>
       <c r="N81" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37511,6 +37596,7 @@
       <c r="L82" s="22"/>
       <c r="M82" s="22"/>
       <c r="N82" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37533,6 +37619,7 @@
       <c r="L83" s="22"/>
       <c r="M83" s="22"/>
       <c r="N83" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37555,6 +37642,7 @@
       <c r="L84" s="22"/>
       <c r="M84" s="22"/>
       <c r="N84" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37577,6 +37665,7 @@
       <c r="L85" s="22"/>
       <c r="M85" s="22"/>
       <c r="N85" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37599,6 +37688,7 @@
       <c r="L86" s="22"/>
       <c r="M86" s="22"/>
       <c r="N86" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37621,6 +37711,7 @@
       <c r="L87" s="22"/>
       <c r="M87" s="22"/>
       <c r="N87" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37643,6 +37734,7 @@
       <c r="L88" s="22"/>
       <c r="M88" s="22"/>
       <c r="N88" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37665,6 +37757,7 @@
       <c r="L89" s="22"/>
       <c r="M89" s="22"/>
       <c r="N89" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37687,6 +37780,7 @@
       <c r="L90" s="22"/>
       <c r="M90" s="22"/>
       <c r="N90" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37709,6 +37803,7 @@
       <c r="L91" s="22"/>
       <c r="M91" s="22"/>
       <c r="N91" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37731,6 +37826,7 @@
       <c r="L92" s="22"/>
       <c r="M92" s="22"/>
       <c r="N92" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37753,6 +37849,7 @@
       <c r="L93" s="22"/>
       <c r="M93" s="22"/>
       <c r="N93" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37777,6 +37874,7 @@
       <c r="L94" s="22"/>
       <c r="M94" s="22"/>
       <c r="N94" s="23">
+        <f t="shared" si="1"/>
         <v>-2.5</v>
       </c>
     </row>
@@ -37801,6 +37899,7 @@
       <c r="L95" s="22"/>
       <c r="M95" s="22"/>
       <c r="N95" s="23">
+        <f t="shared" si="1"/>
         <v>-2.5</v>
       </c>
     </row>
@@ -37825,6 +37924,7 @@
       <c r="L96" s="22"/>
       <c r="M96" s="22"/>
       <c r="N96" s="23">
+        <f t="shared" si="1"/>
         <v>-2.5</v>
       </c>
     </row>
@@ -37847,6 +37947,7 @@
       <c r="L97" s="22"/>
       <c r="M97" s="22"/>
       <c r="N97" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37869,6 +37970,7 @@
       <c r="L98" s="22"/>
       <c r="M98" s="22"/>
       <c r="N98" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37891,6 +37993,7 @@
       <c r="L99" s="22"/>
       <c r="M99" s="22"/>
       <c r="N99" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37913,6 +38016,7 @@
       <c r="L100" s="22"/>
       <c r="M100" s="22"/>
       <c r="N100" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37935,6 +38039,7 @@
       <c r="L101" s="22"/>
       <c r="M101" s="22"/>
       <c r="N101" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37957,6 +38062,7 @@
       <c r="L102" s="22"/>
       <c r="M102" s="22"/>
       <c r="N102" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -37979,6 +38085,7 @@
       <c r="L103" s="22"/>
       <c r="M103" s="22"/>
       <c r="N103" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38001,6 +38108,7 @@
       <c r="L104" s="22"/>
       <c r="M104" s="22"/>
       <c r="N104" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38023,6 +38131,7 @@
       <c r="L105" s="22"/>
       <c r="M105" s="22"/>
       <c r="N105" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38045,6 +38154,7 @@
       <c r="L106" s="22"/>
       <c r="M106" s="22"/>
       <c r="N106" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38067,6 +38177,7 @@
       <c r="L107" s="22"/>
       <c r="M107" s="22"/>
       <c r="N107" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38089,6 +38200,7 @@
       <c r="L108" s="22"/>
       <c r="M108" s="22"/>
       <c r="N108" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38111,6 +38223,7 @@
       <c r="L109" s="22"/>
       <c r="M109" s="22"/>
       <c r="N109" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38133,6 +38246,7 @@
       <c r="L110" s="22"/>
       <c r="M110" s="22"/>
       <c r="N110" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38155,6 +38269,7 @@
       <c r="L111" s="22"/>
       <c r="M111" s="22"/>
       <c r="N111" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38177,6 +38292,7 @@
       <c r="L112" s="22"/>
       <c r="M112" s="22"/>
       <c r="N112" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38199,6 +38315,7 @@
       <c r="L113" s="22"/>
       <c r="M113" s="22"/>
       <c r="N113" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38221,6 +38338,7 @@
       <c r="L114" s="22"/>
       <c r="M114" s="22"/>
       <c r="N114" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38243,6 +38361,7 @@
       <c r="L115" s="22"/>
       <c r="M115" s="22"/>
       <c r="N115" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38265,6 +38384,7 @@
       <c r="L116" s="22"/>
       <c r="M116" s="22"/>
       <c r="N116" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38287,6 +38407,7 @@
       <c r="L117" s="22"/>
       <c r="M117" s="22"/>
       <c r="N117" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38309,6 +38430,7 @@
       <c r="L118" s="22"/>
       <c r="M118" s="22"/>
       <c r="N118" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38331,6 +38453,7 @@
       <c r="L119" s="22"/>
       <c r="M119" s="22"/>
       <c r="N119" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38353,6 +38476,7 @@
       <c r="L120" s="22"/>
       <c r="M120" s="22"/>
       <c r="N120" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38375,6 +38499,7 @@
       <c r="L121" s="22"/>
       <c r="M121" s="22"/>
       <c r="N121" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38397,6 +38522,7 @@
       <c r="L122" s="22"/>
       <c r="M122" s="22"/>
       <c r="N122" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38419,6 +38545,7 @@
       <c r="L123" s="22"/>
       <c r="M123" s="22"/>
       <c r="N123" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38441,6 +38568,7 @@
       <c r="L124" s="22"/>
       <c r="M124" s="22"/>
       <c r="N124" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38463,6 +38591,7 @@
       <c r="L125" s="22"/>
       <c r="M125" s="22"/>
       <c r="N125" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38485,6 +38614,7 @@
       <c r="L126" s="22"/>
       <c r="M126" s="22"/>
       <c r="N126" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38507,6 +38637,7 @@
       <c r="L127" s="22"/>
       <c r="M127" s="22"/>
       <c r="N127" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38529,6 +38660,7 @@
       <c r="L128" s="22"/>
       <c r="M128" s="22"/>
       <c r="N128" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38551,6 +38683,7 @@
       <c r="L129" s="22"/>
       <c r="M129" s="22"/>
       <c r="N129" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38573,6 +38706,7 @@
       <c r="L130" s="22"/>
       <c r="M130" s="22"/>
       <c r="N130" s="23">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -38595,6 +38729,7 @@
       <c r="L131" s="22"/>
       <c r="M131" s="22"/>
       <c r="N131" s="23">
+        <f t="shared" ref="N131:N194" si="2">SUM(C131:M131)</f>
         <v>0</v>
       </c>
     </row>
@@ -38617,6 +38752,7 @@
       <c r="L132" s="22"/>
       <c r="M132" s="22"/>
       <c r="N132" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38639,6 +38775,7 @@
       <c r="L133" s="22"/>
       <c r="M133" s="22"/>
       <c r="N133" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38661,6 +38798,7 @@
       <c r="L134" s="22"/>
       <c r="M134" s="22"/>
       <c r="N134" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38683,6 +38821,7 @@
       <c r="L135" s="22"/>
       <c r="M135" s="22"/>
       <c r="N135" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38705,6 +38844,7 @@
       <c r="L136" s="22"/>
       <c r="M136" s="22"/>
       <c r="N136" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38727,6 +38867,7 @@
       <c r="L137" s="22"/>
       <c r="M137" s="22"/>
       <c r="N137" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38749,6 +38890,7 @@
       <c r="L138" s="22"/>
       <c r="M138" s="22"/>
       <c r="N138" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38771,6 +38913,7 @@
       <c r="L139" s="22"/>
       <c r="M139" s="22"/>
       <c r="N139" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38793,6 +38936,7 @@
       <c r="L140" s="22"/>
       <c r="M140" s="22"/>
       <c r="N140" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38815,6 +38959,7 @@
       <c r="L141" s="22"/>
       <c r="M141" s="22"/>
       <c r="N141" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38837,6 +38982,7 @@
       <c r="L142" s="22"/>
       <c r="M142" s="22"/>
       <c r="N142" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38859,6 +39005,7 @@
       <c r="L143" s="22"/>
       <c r="M143" s="22"/>
       <c r="N143" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38881,6 +39028,7 @@
       <c r="L144" s="22"/>
       <c r="M144" s="22"/>
       <c r="N144" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38903,6 +39051,7 @@
       <c r="L145" s="22"/>
       <c r="M145" s="22"/>
       <c r="N145" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38925,6 +39074,7 @@
       <c r="L146" s="22"/>
       <c r="M146" s="22"/>
       <c r="N146" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38947,6 +39097,7 @@
       <c r="L147" s="22"/>
       <c r="M147" s="22"/>
       <c r="N147" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38969,6 +39120,7 @@
       <c r="L148" s="22"/>
       <c r="M148" s="22"/>
       <c r="N148" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -38991,6 +39143,7 @@
       <c r="L149" s="22"/>
       <c r="M149" s="22"/>
       <c r="N149" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39013,6 +39166,7 @@
       <c r="L150" s="22"/>
       <c r="M150" s="22"/>
       <c r="N150" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39035,6 +39189,7 @@
       <c r="L151" s="22"/>
       <c r="M151" s="22"/>
       <c r="N151" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39057,6 +39212,7 @@
       <c r="L152" s="22"/>
       <c r="M152" s="22"/>
       <c r="N152" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39079,6 +39235,7 @@
       <c r="L153" s="22"/>
       <c r="M153" s="22"/>
       <c r="N153" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39101,6 +39258,7 @@
       <c r="L154" s="22"/>
       <c r="M154" s="22"/>
       <c r="N154" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39123,6 +39281,7 @@
       <c r="L155" s="22"/>
       <c r="M155" s="22"/>
       <c r="N155" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39145,6 +39304,7 @@
       <c r="L156" s="22"/>
       <c r="M156" s="22"/>
       <c r="N156" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39167,6 +39327,7 @@
       <c r="L157" s="22"/>
       <c r="M157" s="22"/>
       <c r="N157" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39189,6 +39350,7 @@
       <c r="L158" s="22"/>
       <c r="M158" s="22"/>
       <c r="N158" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39211,6 +39373,7 @@
       <c r="L159" s="22"/>
       <c r="M159" s="22"/>
       <c r="N159" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39233,6 +39396,7 @@
       <c r="L160" s="22"/>
       <c r="M160" s="22"/>
       <c r="N160" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39255,6 +39419,7 @@
       <c r="L161" s="22"/>
       <c r="M161" s="22"/>
       <c r="N161" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39277,6 +39442,7 @@
       <c r="L162" s="22"/>
       <c r="M162" s="22"/>
       <c r="N162" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39299,6 +39465,7 @@
       <c r="L163" s="22"/>
       <c r="M163" s="22"/>
       <c r="N163" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39321,6 +39488,7 @@
       <c r="L164" s="22"/>
       <c r="M164" s="22"/>
       <c r="N164" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39343,6 +39511,7 @@
       <c r="L165" s="22"/>
       <c r="M165" s="22"/>
       <c r="N165" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39365,6 +39534,7 @@
       <c r="L166" s="22"/>
       <c r="M166" s="22"/>
       <c r="N166" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39387,6 +39557,7 @@
       <c r="L167" s="22"/>
       <c r="M167" s="22"/>
       <c r="N167" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39409,6 +39580,7 @@
       <c r="L168" s="22"/>
       <c r="M168" s="22"/>
       <c r="N168" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39431,6 +39603,7 @@
       <c r="L169" s="22"/>
       <c r="M169" s="22"/>
       <c r="N169" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39453,6 +39626,7 @@
       <c r="L170" s="22"/>
       <c r="M170" s="22"/>
       <c r="N170" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39475,6 +39649,7 @@
       <c r="L171" s="22"/>
       <c r="M171" s="22"/>
       <c r="N171" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39497,6 +39672,7 @@
       <c r="L172" s="22"/>
       <c r="M172" s="22"/>
       <c r="N172" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39519,6 +39695,7 @@
       <c r="L173" s="22"/>
       <c r="M173" s="22"/>
       <c r="N173" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39541,6 +39718,7 @@
       <c r="L174" s="22"/>
       <c r="M174" s="22"/>
       <c r="N174" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39563,6 +39741,7 @@
       <c r="L175" s="22"/>
       <c r="M175" s="22"/>
       <c r="N175" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39585,6 +39764,7 @@
       <c r="L176" s="22"/>
       <c r="M176" s="22"/>
       <c r="N176" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39607,6 +39787,7 @@
       <c r="L177" s="22"/>
       <c r="M177" s="22"/>
       <c r="N177" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39629,6 +39810,7 @@
       <c r="L178" s="22"/>
       <c r="M178" s="22"/>
       <c r="N178" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39651,6 +39833,7 @@
       <c r="L179" s="22"/>
       <c r="M179" s="22"/>
       <c r="N179" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39673,6 +39856,7 @@
       <c r="L180" s="22"/>
       <c r="M180" s="22"/>
       <c r="N180" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39695,6 +39879,7 @@
       <c r="L181" s="22"/>
       <c r="M181" s="22"/>
       <c r="N181" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39717,6 +39902,7 @@
       <c r="L182" s="22"/>
       <c r="M182" s="22"/>
       <c r="N182" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39739,6 +39925,7 @@
       <c r="L183" s="22"/>
       <c r="M183" s="22"/>
       <c r="N183" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39761,6 +39948,7 @@
       <c r="L184" s="22"/>
       <c r="M184" s="22"/>
       <c r="N184" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39783,6 +39971,7 @@
       <c r="L185" s="22"/>
       <c r="M185" s="22"/>
       <c r="N185" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39805,6 +39994,7 @@
       <c r="L186" s="22"/>
       <c r="M186" s="22"/>
       <c r="N186" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39827,6 +40017,7 @@
       <c r="L187" s="22"/>
       <c r="M187" s="22"/>
       <c r="N187" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39849,6 +40040,7 @@
       <c r="L188" s="22"/>
       <c r="M188" s="22"/>
       <c r="N188" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39871,6 +40063,7 @@
       <c r="L189" s="22"/>
       <c r="M189" s="22"/>
       <c r="N189" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39893,6 +40086,7 @@
       <c r="L190" s="22"/>
       <c r="M190" s="22"/>
       <c r="N190" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39915,6 +40109,7 @@
       <c r="L191" s="22"/>
       <c r="M191" s="22"/>
       <c r="N191" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39937,6 +40132,7 @@
       <c r="L192" s="22"/>
       <c r="M192" s="22"/>
       <c r="N192" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39959,6 +40155,7 @@
       <c r="L193" s="22"/>
       <c r="M193" s="22"/>
       <c r="N193" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -39981,6 +40178,7 @@
       <c r="L194" s="22"/>
       <c r="M194" s="22"/>
       <c r="N194" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -40003,6 +40201,7 @@
       <c r="L195" s="22"/>
       <c r="M195" s="22"/>
       <c r="N195" s="23">
+        <f t="shared" ref="N195:N258" si="3">SUM(C195:M195)</f>
         <v>0</v>
       </c>
     </row>
@@ -40025,6 +40224,7 @@
       <c r="L196" s="22"/>
       <c r="M196" s="22"/>
       <c r="N196" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40047,6 +40247,7 @@
       <c r="L197" s="22"/>
       <c r="M197" s="22"/>
       <c r="N197" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40069,6 +40270,7 @@
       <c r="L198" s="22"/>
       <c r="M198" s="22"/>
       <c r="N198" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40091,6 +40293,7 @@
       <c r="L199" s="22"/>
       <c r="M199" s="22"/>
       <c r="N199" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40113,6 +40316,7 @@
       <c r="L200" s="22"/>
       <c r="M200" s="22"/>
       <c r="N200" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40135,6 +40339,7 @@
       <c r="L201" s="22"/>
       <c r="M201" s="22"/>
       <c r="N201" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40157,6 +40362,7 @@
       <c r="L202" s="22"/>
       <c r="M202" s="22"/>
       <c r="N202" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40179,6 +40385,7 @@
       <c r="L203" s="22"/>
       <c r="M203" s="22"/>
       <c r="N203" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40201,6 +40408,7 @@
       <c r="L204" s="22"/>
       <c r="M204" s="22"/>
       <c r="N204" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40223,6 +40431,7 @@
       <c r="L205" s="22"/>
       <c r="M205" s="22"/>
       <c r="N205" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40245,6 +40454,7 @@
       <c r="L206" s="22"/>
       <c r="M206" s="22"/>
       <c r="N206" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40267,6 +40477,7 @@
       <c r="L207" s="22"/>
       <c r="M207" s="22"/>
       <c r="N207" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40289,6 +40500,7 @@
       <c r="L208" s="22"/>
       <c r="M208" s="22"/>
       <c r="N208" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40311,6 +40523,7 @@
       <c r="L209" s="22"/>
       <c r="M209" s="22"/>
       <c r="N209" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40333,6 +40546,7 @@
       <c r="L210" s="22"/>
       <c r="M210" s="22"/>
       <c r="N210" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40355,6 +40569,7 @@
       <c r="L211" s="22"/>
       <c r="M211" s="22"/>
       <c r="N211" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40377,6 +40592,7 @@
       <c r="L212" s="22"/>
       <c r="M212" s="22"/>
       <c r="N212" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40399,6 +40615,7 @@
       <c r="L213" s="22"/>
       <c r="M213" s="22"/>
       <c r="N213" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40421,6 +40638,7 @@
       <c r="L214" s="22"/>
       <c r="M214" s="22"/>
       <c r="N214" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40443,6 +40661,7 @@
       <c r="L215" s="22"/>
       <c r="M215" s="22"/>
       <c r="N215" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40465,6 +40684,7 @@
       <c r="L216" s="22"/>
       <c r="M216" s="22"/>
       <c r="N216" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40487,6 +40707,7 @@
       <c r="L217" s="22"/>
       <c r="M217" s="22"/>
       <c r="N217" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40509,6 +40730,7 @@
       <c r="L218" s="22"/>
       <c r="M218" s="22"/>
       <c r="N218" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40531,6 +40753,7 @@
       <c r="L219" s="22"/>
       <c r="M219" s="22"/>
       <c r="N219" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40553,6 +40776,7 @@
       <c r="L220" s="22"/>
       <c r="M220" s="22"/>
       <c r="N220" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40575,6 +40799,7 @@
       <c r="L221" s="22"/>
       <c r="M221" s="22"/>
       <c r="N221" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40597,6 +40822,7 @@
       <c r="L222" s="22"/>
       <c r="M222" s="22"/>
       <c r="N222" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40619,6 +40845,7 @@
       <c r="L223" s="22"/>
       <c r="M223" s="22"/>
       <c r="N223" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40641,6 +40868,7 @@
       <c r="L224" s="22"/>
       <c r="M224" s="22"/>
       <c r="N224" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40663,6 +40891,7 @@
       <c r="L225" s="22"/>
       <c r="M225" s="22"/>
       <c r="N225" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40685,6 +40914,7 @@
       <c r="L226" s="22"/>
       <c r="M226" s="22"/>
       <c r="N226" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40707,6 +40937,7 @@
       <c r="L227" s="22"/>
       <c r="M227" s="22"/>
       <c r="N227" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40729,6 +40960,7 @@
       <c r="L228" s="22"/>
       <c r="M228" s="22"/>
       <c r="N228" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40751,6 +40983,7 @@
       <c r="L229" s="22"/>
       <c r="M229" s="22"/>
       <c r="N229" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40773,6 +41006,7 @@
       <c r="L230" s="22"/>
       <c r="M230" s="22"/>
       <c r="N230" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40795,6 +41029,7 @@
       <c r="L231" s="22"/>
       <c r="M231" s="22"/>
       <c r="N231" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40817,6 +41052,7 @@
       <c r="L232" s="22"/>
       <c r="M232" s="22"/>
       <c r="N232" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40839,6 +41075,7 @@
       <c r="L233" s="22"/>
       <c r="M233" s="22"/>
       <c r="N233" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40861,6 +41098,7 @@
       <c r="L234" s="22"/>
       <c r="M234" s="22"/>
       <c r="N234" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40883,6 +41121,7 @@
       <c r="L235" s="22"/>
       <c r="M235" s="22"/>
       <c r="N235" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40905,6 +41144,7 @@
       <c r="L236" s="22"/>
       <c r="M236" s="22"/>
       <c r="N236" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40927,6 +41167,7 @@
       <c r="L237" s="22"/>
       <c r="M237" s="22"/>
       <c r="N237" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40949,6 +41190,7 @@
       <c r="L238" s="22"/>
       <c r="M238" s="22"/>
       <c r="N238" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40971,6 +41213,7 @@
       <c r="L239" s="22"/>
       <c r="M239" s="22"/>
       <c r="N239" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40993,6 +41236,7 @@
       <c r="L240" s="22"/>
       <c r="M240" s="22"/>
       <c r="N240" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41015,6 +41259,7 @@
       <c r="L241" s="22"/>
       <c r="M241" s="22"/>
       <c r="N241" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41037,6 +41282,7 @@
       <c r="L242" s="22"/>
       <c r="M242" s="22"/>
       <c r="N242" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41059,6 +41305,7 @@
       <c r="L243" s="22"/>
       <c r="M243" s="22"/>
       <c r="N243" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41081,6 +41328,7 @@
       <c r="L244" s="22"/>
       <c r="M244" s="22"/>
       <c r="N244" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41103,6 +41351,7 @@
       <c r="L245" s="22"/>
       <c r="M245" s="22"/>
       <c r="N245" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41127,6 +41376,7 @@
       <c r="L246" s="22"/>
       <c r="M246" s="22"/>
       <c r="N246" s="23">
+        <f t="shared" si="3"/>
         <v>-2.5</v>
       </c>
     </row>
@@ -41149,6 +41399,7 @@
       <c r="L247" s="22"/>
       <c r="M247" s="22"/>
       <c r="N247" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41171,6 +41422,7 @@
       <c r="L248" s="22"/>
       <c r="M248" s="22"/>
       <c r="N248" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41193,6 +41445,7 @@
       <c r="L249" s="22"/>
       <c r="M249" s="22"/>
       <c r="N249" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41215,6 +41468,7 @@
       <c r="L250" s="22"/>
       <c r="M250" s="22"/>
       <c r="N250" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41237,6 +41491,7 @@
       <c r="L251" s="22"/>
       <c r="M251" s="22"/>
       <c r="N251" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41259,6 +41514,7 @@
       <c r="L252" s="22"/>
       <c r="M252" s="22"/>
       <c r="N252" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41281,6 +41537,7 @@
       <c r="L253" s="22"/>
       <c r="M253" s="22"/>
       <c r="N253" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41303,6 +41560,7 @@
       <c r="L254" s="22"/>
       <c r="M254" s="22"/>
       <c r="N254" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41325,6 +41583,7 @@
       <c r="L255" s="22"/>
       <c r="M255" s="22"/>
       <c r="N255" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41347,6 +41606,7 @@
       <c r="L256" s="22"/>
       <c r="M256" s="22"/>
       <c r="N256" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41369,6 +41629,7 @@
       <c r="L257" s="22"/>
       <c r="M257" s="22"/>
       <c r="N257" s="23">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -41393,6 +41654,7 @@
       <c r="L258" s="22"/>
       <c r="M258" s="22"/>
       <c r="N258" s="23">
+        <f t="shared" si="3"/>
         <v>-2.5</v>
       </c>
     </row>
@@ -41415,6 +41677,7 @@
       <c r="L259" s="22"/>
       <c r="M259" s="22"/>
       <c r="N259" s="23">
+        <f t="shared" ref="N259:N286" si="4">SUM(C259:M259)</f>
         <v>0</v>
       </c>
     </row>
@@ -41437,6 +41700,7 @@
       <c r="L260" s="22"/>
       <c r="M260" s="22"/>
       <c r="N260" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41459,6 +41723,7 @@
       <c r="L261" s="22"/>
       <c r="M261" s="22"/>
       <c r="N261" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41481,6 +41746,7 @@
       <c r="L262" s="22"/>
       <c r="M262" s="22"/>
       <c r="N262" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41503,6 +41769,7 @@
       <c r="L263" s="22"/>
       <c r="M263" s="22"/>
       <c r="N263" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41525,6 +41792,7 @@
       <c r="L264" s="22"/>
       <c r="M264" s="22"/>
       <c r="N264" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41547,6 +41815,7 @@
       <c r="L265" s="22"/>
       <c r="M265" s="22"/>
       <c r="N265" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41569,6 +41838,7 @@
       <c r="L266" s="22"/>
       <c r="M266" s="22"/>
       <c r="N266" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41591,6 +41861,7 @@
       <c r="L267" s="22"/>
       <c r="M267" s="22"/>
       <c r="N267" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41613,6 +41884,7 @@
       <c r="L268" s="22"/>
       <c r="M268" s="22"/>
       <c r="N268" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41635,6 +41907,7 @@
       <c r="L269" s="22"/>
       <c r="M269" s="22"/>
       <c r="N269" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41657,6 +41930,7 @@
       <c r="L270" s="22"/>
       <c r="M270" s="22"/>
       <c r="N270" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41679,6 +41953,7 @@
       <c r="L271" s="22"/>
       <c r="M271" s="22"/>
       <c r="N271" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41703,6 +41978,7 @@
       <c r="L272" s="22"/>
       <c r="M272" s="22"/>
       <c r="N272" s="23">
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
     </row>
@@ -41725,6 +42001,7 @@
       <c r="L273" s="22"/>
       <c r="M273" s="22"/>
       <c r="N273" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41747,6 +42024,7 @@
       <c r="L274" s="22"/>
       <c r="M274" s="22"/>
       <c r="N274" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41769,6 +42047,7 @@
       <c r="L275" s="22"/>
       <c r="M275" s="22"/>
       <c r="N275" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41791,6 +42070,7 @@
       <c r="L276" s="22"/>
       <c r="M276" s="22"/>
       <c r="N276" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41813,6 +42093,7 @@
       <c r="L277" s="22"/>
       <c r="M277" s="22"/>
       <c r="N277" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41835,6 +42116,7 @@
       <c r="L278" s="22"/>
       <c r="M278" s="22"/>
       <c r="N278" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41857,6 +42139,7 @@
       <c r="L279" s="22"/>
       <c r="M279" s="22"/>
       <c r="N279" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41879,6 +42162,7 @@
       <c r="L280" s="22"/>
       <c r="M280" s="22"/>
       <c r="N280" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41901,6 +42185,7 @@
       <c r="L281" s="22"/>
       <c r="M281" s="22"/>
       <c r="N281" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41923,6 +42208,7 @@
       <c r="L282" s="22"/>
       <c r="M282" s="22"/>
       <c r="N282" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41945,6 +42231,7 @@
       <c r="L283" s="22"/>
       <c r="M283" s="22"/>
       <c r="N283" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41967,6 +42254,7 @@
       <c r="L284" s="22"/>
       <c r="M284" s="22"/>
       <c r="N284" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -41989,6 +42277,7 @@
       <c r="L285" s="22"/>
       <c r="M285" s="22"/>
       <c r="N285" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -42011,6 +42300,7 @@
       <c r="L286" s="22"/>
       <c r="M286" s="22"/>
       <c r="N286" s="23">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -42026,6 +42316,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N287" xr:uid="{A79528FD-BC0F-4865-9E8B-3AB306CAC368}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
